--- a/Schibsted modell.xlsx
+++ b/Schibsted modell.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/augusthodt/Desktop/Aksjemodellering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA0C5FE5-13E4-FD45-8833-960E68D6675C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBF1C615-B6D7-CA42-A4FB-0AE5F6A18F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17200" xr2:uid="{CF2EC152-6970-7944-95E4-562C87096A91}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17220" activeTab="1" xr2:uid="{CF2EC152-6970-7944-95E4-562C87096A91}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -170,6 +170,9 @@
   <authors>
     <author>tc={2EDCE919-97FE-3C4A-9ED1-492F491396BC}</author>
     <author>tc={5721A1CA-DAD0-6D4C-931E-50DA55EB8D05}</author>
+    <author>tc={47370B81-A1A0-7946-B0FE-FCABF156DC86}</author>
+    <author>tc={855CE0B9-BC63-6348-846F-F9982993BC6D}</author>
+    <author>tc={681C1A77-2E6E-6149-A4EC-4992728B70CF}</author>
     <author>august hodt</author>
   </authors>
   <commentList>
@@ -190,7 +193,31 @@
 </t>
       </text>
     </comment>
-    <comment ref="U22" authorId="2" shapeId="0" xr:uid="{2E231A30-FD59-F54E-9238-4034B6230763}">
+    <comment ref="AC4" authorId="2" shapeId="0" xr:uid="{47370B81-A1A0-7946-B0FE-FCABF156DC86}">
+      <text>
+        <t>[Kommentartråd]
+Din versjon av Excel lar deg lese denne kommentartråden. Eventuelle endringer i den vil imidlertid bli fjernet hvis filen åpnes i en nyere versjon av Excel. Finn ut mer: https://go.microsoft.com/fwlink/?linkid=870924
+Kommentar:
+    Juli-august</t>
+      </text>
+    </comment>
+    <comment ref="AD4" authorId="3" shapeId="0" xr:uid="{855CE0B9-BC63-6348-846F-F9982993BC6D}">
+      <text>
+        <t>[Kommentartråd]
+Din versjon av Excel lar deg lese denne kommentartråden. Eventuelle endringer i den vil imidlertid bli fjernet hvis filen åpnes i en nyere versjon av Excel. Finn ut mer: https://go.microsoft.com/fwlink/?linkid=870924
+Kommentar:
+    Oktober-november</t>
+      </text>
+    </comment>
+    <comment ref="C18" authorId="4" shapeId="0" xr:uid="{681C1A77-2E6E-6149-A4EC-4992728B70CF}">
+      <text>
+        <t>[Kommentartråd]
+Din versjon av Excel lar deg lese denne kommentartråden. Eventuelle endringer i den vil imidlertid bli fjernet hvis filen åpnes i en nyere versjon av Excel. Finn ut mer: https://go.microsoft.com/fwlink/?linkid=870924
+Kommentar:
+    Le på antall listede boliger fra eiendomNorge</t>
+      </text>
+    </comment>
+    <comment ref="U22" authorId="5" shapeId="0" xr:uid="{2E231A30-FD59-F54E-9238-4034B6230763}">
       <text>
         <r>
           <rPr>
@@ -256,7 +283,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="348">
   <si>
     <t>Kapitalstruktur</t>
   </si>
@@ -529,9 +556,6 @@
   </si>
   <si>
     <t>Total E/D</t>
-  </si>
-  <si>
-    <t>cash Flow NOKm</t>
   </si>
   <si>
     <t>CFFO</t>
@@ -1352,6 +1376,57 @@
   </si>
   <si>
     <t>27.07.26: Vend kjøper tilbake 603 000 aksjer</t>
+  </si>
+  <si>
+    <t>03.08.26: Vend kjøper tilbake 560 000 aksjer</t>
+  </si>
+  <si>
+    <t>06.08.26: Vend kjøper tilbake 175 547 aksjer og fullfører første transje av tilbakekjøpsprogrammet</t>
+  </si>
+  <si>
+    <t>06.08.26: Vend starter andre transje av tilbakekjøpsprogrammet</t>
+  </si>
+  <si>
+    <t>Cash Flow NOKm</t>
+  </si>
+  <si>
+    <t>11.08.26: Vend kjøper tilbake 263 000 aksjer</t>
+  </si>
+  <si>
+    <t>Transje 1</t>
+  </si>
+  <si>
+    <t>Transje 2</t>
+  </si>
+  <si>
+    <t>17.08.26: Vend kjøper tilbake 591 000 aksjer</t>
+  </si>
+  <si>
+    <t>24.08.26: Vend kjøper tilbake 400 000 aksjer</t>
+  </si>
+  <si>
+    <t>31.08.26: Vend kjøper tilbake 210 000 aksjer</t>
+  </si>
+  <si>
+    <t>07.09.26. Vend kjøper tilbake 286 000 aksjer</t>
+  </si>
+  <si>
+    <t>Liten øker 15%</t>
+  </si>
+  <si>
+    <t>Medium øker 20%</t>
+  </si>
+  <si>
+    <t>Stor øker 5%</t>
+  </si>
+  <si>
+    <t>Antar 60/40 mellom med og stor</t>
+  </si>
+  <si>
+    <t>Innebører en arpa vekst på 11% i 2027</t>
+  </si>
+  <si>
+    <t>14.09.26: Vend kjøper tilbake 328 000 aksjer</t>
   </si>
 </sst>
 </file>
@@ -1809,7 +1884,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1951,10 +2026,15 @@
     <xf numFmtId="173" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="172" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperkobling" xfId="1" builtinId="8"/>
@@ -3145,6 +3225,15 @@
     <text xml:space="preserve">April-mai
 </text>
   </threadedComment>
+  <threadedComment ref="AC4" dT="2026-09-01T18:39:14.16" personId="{53D900F6-2C25-4947-A6FB-0AC1CDDED5CD}" id="{47370B81-A1A0-7946-B0FE-FCABF156DC86}">
+    <text>Juli-august</text>
+  </threadedComment>
+  <threadedComment ref="AD4" dT="2026-09-14T06:44:18.64" personId="{53D900F6-2C25-4947-A6FB-0AC1CDDED5CD}" id="{855CE0B9-BC63-6348-846F-F9982993BC6D}">
+    <text>Oktober-november</text>
+  </threadedComment>
+  <threadedComment ref="C18" dT="2026-09-14T06:51:24.59" personId="{53D900F6-2C25-4947-A6FB-0AC1CDDED5CD}" id="{681C1A77-2E6E-6149-A4EC-4992728B70CF}">
+    <text>Le på antall listede boliger fra eiendomNorge</text>
+  </threadedComment>
 </ThreadedComments>
 </file>
 
@@ -3175,7 +3264,6 @@
     <we:reference id="wa200009404" version="1.0.0.5" store="nb-NO" storeType="OMEX"/>
   </we:alternateReferences>
   <we:properties>
-    <we:property name="Office.AutoShowTaskpaneWithDocument" value="true"/>
     <we:property name="claude.fileId" value="&quot;b59386d4-b6cf-4e88-9101-80d85e2939a8&quot;"/>
   </we:properties>
   <we:bindings/>
@@ -3185,7 +3273,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17698142-E94C-684E-8A27-765BEE6464F1}">
-  <dimension ref="A1:AA77"/>
+  <dimension ref="A1:AA86"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.83203125" style="1" bestFit="1" customWidth="1"/>
@@ -3206,7 +3294,7 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="H1" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
@@ -3216,7 +3304,7 @@
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="H2" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
@@ -3226,7 +3314,7 @@
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="H3" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
@@ -3236,7 +3324,7 @@
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="H4" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
@@ -3253,13 +3341,13 @@
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="H6" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
@@ -3268,33 +3356,33 @@
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="H7" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="U7" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="V7" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="V7" s="2" t="s">
+      <c r="W7" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="X7" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="X7" s="2" t="s">
+      <c r="Y7" s="2" t="s">
         <v>261</v>
-      </c>
-      <c r="Y7" s="2" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="H8" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="U8" s="67">
         <v>45993</v>
@@ -3316,7 +3404,7 @@
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="H9" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="U9" s="67">
         <v>45999</v>
@@ -3359,7 +3447,7 @@
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="H11" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="U11" s="67">
         <v>46011</v>
@@ -3382,7 +3470,7 @@
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="H12" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="U12" s="67">
         <v>46020</v>
@@ -3405,7 +3493,7 @@
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="H13" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="U13" s="67">
         <v>46027</v>
@@ -3428,7 +3516,7 @@
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="H14" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="U14" s="67">
         <v>46034</v>
@@ -3438,7 +3526,7 @@
       </c>
       <c r="W14" s="14">
         <f>SUM(V8:V149)</f>
-        <v>15594983</v>
+        <v>17830530</v>
       </c>
       <c r="X14" s="14">
         <f>532167563-Y13</f>
@@ -3451,7 +3539,7 @@
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="U15" s="67">
         <v>46041</v>
@@ -3474,7 +3562,7 @@
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="U16" s="67">
         <v>46048</v>
@@ -3517,7 +3605,7 @@
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N18" s="47" t="s">
         <v>52</v>
@@ -3555,22 +3643,22 @@
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="N19" s="48" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O19" s="48" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P19" s="48" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q19" s="48" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R19" s="48" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="U19" s="67">
         <v>46069</v>
@@ -3593,19 +3681,19 @@
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N20" s="48" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O20" s="48" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P20" s="48" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q20" s="48" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R20" s="48"/>
       <c r="U20" s="67">
@@ -3629,17 +3717,17 @@
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N21" s="48" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O21" s="48"/>
       <c r="P21" s="48" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q21" s="48" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="R21" s="48"/>
       <c r="U21" s="67">
@@ -3663,17 +3751,17 @@
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N22" s="48" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O22" s="48"/>
       <c r="P22" s="48" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q22" s="48" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="R22" s="48"/>
       <c r="U22" s="67">
@@ -3697,7 +3785,7 @@
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="N23" s="48" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O23" s="48"/>
       <c r="Q23" s="48"/>
@@ -3723,7 +3811,7 @@
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="N24" s="48" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="O24" s="48"/>
       <c r="P24" s="48"/>
@@ -3750,7 +3838,7 @@
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="N25" s="48" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="O25" s="48"/>
       <c r="P25" s="48"/>
@@ -3777,10 +3865,10 @@
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N26" s="48" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O26" s="48"/>
       <c r="P26" s="48"/>
@@ -3808,10 +3896,10 @@
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="N27" s="48" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O27" s="49"/>
       <c r="P27" s="49"/>
@@ -3825,7 +3913,10 @@
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>330</v>
+        <v>341</v>
+      </c>
+      <c r="T28" s="1" t="s">
+        <v>336</v>
       </c>
       <c r="U28" s="93">
         <v>46153</v>
@@ -3846,8 +3937,8 @@
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>315</v>
+      <c r="A29" s="67" t="s">
+        <v>340</v>
       </c>
       <c r="U29" s="93">
         <v>46160</v>
@@ -3870,7 +3961,7 @@
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="U30" s="93">
         <v>46168</v>
@@ -3892,7 +3983,7 @@
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>312</v>
+        <v>338</v>
       </c>
       <c r="U31" s="93">
         <v>46174</v>
@@ -3914,7 +4005,7 @@
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>310</v>
+        <v>335</v>
       </c>
       <c r="U32" s="93">
         <v>46181</v>
@@ -3935,8 +4026,8 @@
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A33" s="67" t="s">
-        <v>288</v>
+      <c r="A33" s="1" t="s">
+        <v>333</v>
       </c>
       <c r="U33" s="93">
         <v>46188</v>
@@ -3958,7 +4049,7 @@
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>287</v>
+        <v>332</v>
       </c>
       <c r="U34" s="93">
         <v>46195</v>
@@ -3980,7 +4071,7 @@
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>286</v>
+        <v>331</v>
       </c>
       <c r="U35" s="93">
         <v>46202</v>
@@ -4002,7 +4093,7 @@
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>285</v>
+        <v>330</v>
       </c>
       <c r="U36" s="93">
         <v>46209</v>
@@ -4024,7 +4115,7 @@
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>284</v>
+        <v>329</v>
       </c>
       <c r="U37" s="93">
         <v>46216</v>
@@ -4046,7 +4137,7 @@
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>283</v>
+        <v>314</v>
       </c>
       <c r="U38" s="93">
         <v>46223</v>
@@ -4068,7 +4159,7 @@
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>282</v>
+        <v>313</v>
       </c>
       <c r="U39" s="93">
         <v>46230</v>
@@ -4090,7 +4181,7 @@
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="U40" s="93">
         <v>46237</v>
@@ -4113,203 +4204,373 @@
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="V41" s="15"/>
+        <v>309</v>
+      </c>
+      <c r="U41" s="93">
+        <v>46240</v>
+      </c>
+      <c r="V41" s="14">
+        <v>175547</v>
+      </c>
+      <c r="W41" s="14">
+        <f>SUM(V28:V41)</f>
+        <v>8267547</v>
+      </c>
+      <c r="X41" s="14">
+        <v>42900586</v>
+      </c>
+      <c r="Y41" s="14">
+        <f>SUM(X28:X41)</f>
+        <v>1999999872</v>
+      </c>
       <c r="AA41" s="69"/>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="V42" s="15"/>
+      <c r="A42" s="67" t="s">
+        <v>287</v>
+      </c>
+      <c r="U42" s="122"/>
+      <c r="V42" s="123"/>
+      <c r="W42" s="124"/>
+      <c r="X42" s="124"/>
+      <c r="Y42" s="124"/>
       <c r="AA42" s="70"/>
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>264</v>
+        <v>286</v>
+      </c>
+      <c r="T43" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="U43" s="93">
+        <v>46244</v>
+      </c>
+      <c r="V43" s="14">
+        <v>263000</v>
+      </c>
+      <c r="W43" s="14">
+        <f>V43</f>
+        <v>263000</v>
+      </c>
+      <c r="X43" s="14">
+        <v>64394860</v>
+      </c>
+      <c r="Y43" s="14">
+        <f>X43</f>
+        <v>64394860</v>
       </c>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>263</v>
+        <v>285</v>
+      </c>
+      <c r="U44" s="93">
+        <v>46251</v>
+      </c>
+      <c r="V44" s="14">
+        <v>591000</v>
+      </c>
+      <c r="W44" s="14">
+        <f>SUM(V43:V44)</f>
+        <v>854000</v>
+      </c>
+      <c r="X44" s="14">
+        <v>145454868</v>
+      </c>
+      <c r="Y44" s="14">
+        <f>SUM(X43:X44)</f>
+        <v>209849728</v>
       </c>
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>256</v>
+        <v>284</v>
+      </c>
+      <c r="U45" s="93">
+        <v>46258</v>
+      </c>
+      <c r="V45" s="14">
+        <v>400000</v>
+      </c>
+      <c r="W45" s="14">
+        <f>SUM(V43:V45)</f>
+        <v>1254000</v>
+      </c>
+      <c r="X45" s="14">
+        <v>99156697</v>
+      </c>
+      <c r="Y45" s="14">
+        <f>SUM(X43:X45)</f>
+        <v>309006425</v>
       </c>
     </row>
     <row r="46" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
+      </c>
+      <c r="U46" s="93">
+        <v>46265</v>
+      </c>
+      <c r="V46" s="14">
+        <v>210000</v>
+      </c>
+      <c r="W46" s="14">
+        <f>SUM(V43:V46)</f>
+        <v>1464000</v>
+      </c>
+      <c r="X46" s="14">
+        <v>54369915</v>
+      </c>
+      <c r="Y46" s="14">
+        <f>SUM(X43:X46)</f>
+        <v>363376340</v>
       </c>
     </row>
     <row r="47" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>254</v>
+        <v>282</v>
+      </c>
+      <c r="U47" s="93">
+        <v>46272</v>
+      </c>
+      <c r="V47" s="14">
+        <v>268000</v>
+      </c>
+      <c r="W47" s="14">
+        <f>SUM(V43:V47)</f>
+        <v>1732000</v>
+      </c>
+      <c r="X47" s="14">
+        <v>71677964</v>
+      </c>
+      <c r="Y47" s="14">
+        <f>SUM(X43:X47)</f>
+        <v>435054304</v>
       </c>
     </row>
     <row r="48" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>253</v>
+        <v>281</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
+      </c>
+      <c r="U48" s="93">
+        <v>46278</v>
+      </c>
+      <c r="V48" s="14">
+        <v>328000</v>
+      </c>
+      <c r="W48" s="14">
+        <f>SUM(V43:V48)</f>
+        <v>2060000</v>
+      </c>
+      <c r="X48" s="14">
+        <v>78509529</v>
+      </c>
+      <c r="Y48" s="14">
+        <f>SUM(X43:X48)</f>
+        <v>513563833</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>251</v>
+        <v>280</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>252</v>
+        <v>279</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>231</v>
+        <v>312</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>230</v>
+        <v>263</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>229</v>
+        <v>262</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>228</v>
+        <v>255</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>227</v>
+        <v>254</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>222</v>
+        <v>253</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>221</v>
+        <v>252</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>219</v>
+        <v>251</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>176</v>
+        <v>228</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>201</v>
+        <v>227</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>202</v>
+        <v>226</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>209</v>
+        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>215</v>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -4329,7 +4590,9 @@
     <col min="1" max="1" width="15.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="4"/>
     <col min="3" max="3" width="39.1640625" style="1" customWidth="1"/>
-    <col min="4" max="32" width="10.83203125" style="1"/>
+    <col min="4" max="22" width="10.83203125" style="1"/>
+    <col min="23" max="23" width="11.6640625" style="1" customWidth="1"/>
+    <col min="24" max="32" width="10.83203125" style="1"/>
     <col min="33" max="33" width="10.83203125" style="4"/>
     <col min="34" max="43" width="10.83203125" style="1"/>
     <col min="44" max="44" width="14.1640625" style="1" bestFit="1" customWidth="1"/>
@@ -4381,39 +4644,39 @@
         <v>17</v>
       </c>
       <c r="P3" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q3" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="Q3" s="13" t="s">
+      <c r="R3" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="R3" s="13" t="s">
+      <c r="S3" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="S3" s="13" t="s">
-        <v>101</v>
-      </c>
       <c r="T3" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="U3" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="U3" s="13" t="s">
+      <c r="V3" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="V3" s="13" t="s">
+      <c r="W3" s="13" t="s">
         <v>225</v>
-      </c>
-      <c r="W3" s="13" t="s">
-        <v>226</v>
       </c>
       <c r="X3" s="13"/>
       <c r="Y3" s="13"/>
       <c r="Z3" s="13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA3" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AB3" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AC3" s="13" t="s">
         <v>18</v>
@@ -4463,7 +4726,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="4">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>52</v>
@@ -4554,7 +4817,7 @@
         <v>32</v>
       </c>
       <c r="B5" s="5">
-        <v>213</v>
+        <v>201.887</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>53</v>
@@ -4646,7 +4909,7 @@
       </c>
       <c r="B6" s="6">
         <f>B4*B5</f>
-        <v>50694</v>
+        <v>47847.218999999997</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>54</v>
@@ -4935,7 +5198,7 @@
       </c>
       <c r="B9" s="7">
         <f>B6-B7+B8</f>
-        <v>48716</v>
+        <v>45869.218999999997</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>59</v>
@@ -5261,11 +5524,11 @@
     </row>
     <row r="12" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B12" s="40">
         <f>B4/(U65/B5)</f>
-        <v>3.0841394415039241</v>
+        <v>2.9109459755429823</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>34</v>
@@ -5392,7 +5655,7 @@
     </row>
     <row r="13" spans="1:42" x14ac:dyDescent="0.25">
       <c r="C13" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D13" s="14">
         <f t="shared" ref="D13:N13" si="4">SUM(D11:D12)</f>
@@ -5541,7 +5804,7 @@
     </row>
     <row r="14" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B14" s="40">
         <f>(B8-B7)/AG17</f>
@@ -5920,7 +6183,7 @@
     </row>
     <row r="17" spans="3:159" x14ac:dyDescent="0.25">
       <c r="C17" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D17" s="15">
         <f t="shared" ref="D17:N17" si="15">SUM(D13:D16)</f>
@@ -5994,8 +6257,14 @@
         <f t="shared" si="16"/>
         <v>674</v>
       </c>
-      <c r="V17" s="15"/>
-      <c r="W17" s="119"/>
+      <c r="V17" s="15">
+        <f>R17*1.14</f>
+        <v>728.45999999999992</v>
+      </c>
+      <c r="W17" s="15">
+        <f>S17*1.14</f>
+        <v>560.88</v>
+      </c>
       <c r="X17" s="15"/>
       <c r="Y17" s="71"/>
       <c r="Z17" s="15">
@@ -6563,7 +6832,7 @@
     </row>
     <row r="22" spans="3:159" x14ac:dyDescent="0.25">
       <c r="C22" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D22" s="15">
         <f t="shared" ref="D22:U22" si="23">SUM(D17:D21)</f>
@@ -7424,7 +7693,7 @@
     </row>
     <row r="29" spans="3:159" x14ac:dyDescent="0.25">
       <c r="C29" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D29" s="14">
         <v>-45</v>
@@ -7622,7 +7891,7 @@
         <v>411</v>
       </c>
       <c r="V30" s="15"/>
-      <c r="W30" s="15"/>
+      <c r="W30" s="14"/>
       <c r="X30" s="15"/>
       <c r="Y30" s="14"/>
       <c r="Z30" s="15">
@@ -8236,7 +8505,7 @@
       </c>
       <c r="U31" s="9">
         <f t="shared" si="43"/>
-        <v>1.9816779170684666</v>
+        <v>2.0357922996527762</v>
       </c>
       <c r="V31" s="9"/>
       <c r="W31" s="9"/>
@@ -8271,43 +8540,43 @@
       </c>
       <c r="AG31" s="40">
         <f t="shared" ref="AG31:AP31" si="45">AG30/AG32</f>
-        <v>5.7095744262295067</v>
+        <v>5.8654878025826314</v>
       </c>
       <c r="AH31" s="9">
         <f t="shared" si="45"/>
-        <v>7.8105666833172629</v>
+        <v>8.0238526013066735</v>
       </c>
       <c r="AI31" s="9">
         <f t="shared" si="45"/>
-        <v>10.336405271016394</v>
+        <v>10.618665160256976</v>
       </c>
       <c r="AJ31" s="9">
         <f t="shared" si="45"/>
-        <v>13.716288774146726</v>
+        <v>14.090844342419429</v>
       </c>
       <c r="AK31" s="9">
         <f t="shared" si="45"/>
-        <v>16.337160275815602</v>
+        <v>16.78328491286787</v>
       </c>
       <c r="AL31" s="9">
         <f t="shared" si="45"/>
-        <v>19.393002176146258</v>
+        <v>19.922573773114337</v>
       </c>
       <c r="AM31" s="9">
         <f t="shared" si="45"/>
-        <v>22.95133420509314</v>
+        <v>23.578074438355699</v>
       </c>
       <c r="AN31" s="9">
         <f t="shared" si="45"/>
-        <v>27.089774955395331</v>
+        <v>27.82952505980569</v>
       </c>
       <c r="AO31" s="9">
         <f t="shared" si="45"/>
-        <v>31.897518867611502</v>
+        <v>32.768555742284676</v>
       </c>
       <c r="AP31" s="9">
         <f t="shared" si="45"/>
-        <v>37.477026175560972</v>
+        <v>38.500424637600958</v>
       </c>
     </row>
     <row r="32" spans="3:159" x14ac:dyDescent="0.25">
@@ -8366,7 +8635,7 @@
         <v>207.4</v>
       </c>
       <c r="U32" s="8">
-        <v>207.4</v>
+        <v>201.887</v>
       </c>
       <c r="V32" s="8"/>
       <c r="W32" s="8"/>
@@ -8393,39 +8662,39 @@
         <v>239</v>
       </c>
       <c r="AG32" s="5">
-        <v>207.4</v>
+        <v>201.887</v>
       </c>
       <c r="AH32" s="8">
-        <v>207.4</v>
+        <v>201.887</v>
       </c>
       <c r="AI32" s="8">
-        <v>207.4</v>
+        <v>201.887</v>
       </c>
       <c r="AJ32" s="8">
-        <v>207.4</v>
+        <v>201.887</v>
       </c>
       <c r="AK32" s="8">
-        <v>207.4</v>
+        <v>201.887</v>
       </c>
       <c r="AL32" s="8">
-        <v>207.4</v>
+        <v>201.887</v>
       </c>
       <c r="AM32" s="8">
-        <v>207.4</v>
+        <v>201.887</v>
       </c>
       <c r="AN32" s="8">
-        <v>207.4</v>
+        <v>201.887</v>
       </c>
       <c r="AO32" s="8">
-        <v>207.4</v>
+        <v>201.887</v>
       </c>
       <c r="AP32" s="8">
-        <v>207.4</v>
+        <v>201.887</v>
       </c>
     </row>
     <row r="33" spans="2:45" x14ac:dyDescent="0.25">
       <c r="AR33" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AS33" s="44">
         <v>0.08</v>
@@ -8495,27 +8764,33 @@
         <f t="shared" si="48"/>
         <v>5.8997050147492625E-4</v>
       </c>
-      <c r="V34" s="18"/>
-      <c r="W34" s="18"/>
+      <c r="V34" s="18">
+        <f t="shared" ref="V34" si="49">(V11-R11)/R11</f>
+        <v>-1</v>
+      </c>
+      <c r="W34" s="18">
+        <f t="shared" ref="W34" si="50">(W11-S11)/S11</f>
+        <v>-1</v>
+      </c>
       <c r="X34" s="18"/>
       <c r="AA34" s="18">
-        <f t="shared" ref="AA34:AE34" si="49">(AA11-Z11)/Z11</f>
+        <f t="shared" ref="AA34:AE34" si="51">(AA11-Z11)/Z11</f>
         <v>2.0153323322532207E-2</v>
       </c>
       <c r="AB34" s="18">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0.13286334056399132</v>
       </c>
       <c r="AC34" s="18">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>4.4382137728236341E-2</v>
       </c>
       <c r="AD34" s="18">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>-0.50124410686223153</v>
       </c>
       <c r="AE34" s="18">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>9.2949980307207566E-2</v>
       </c>
       <c r="AF34" s="18">
@@ -8523,47 +8798,47 @@
         <v>-0.2412012012012012</v>
       </c>
       <c r="AG34" s="19">
-        <f t="shared" ref="AG34:AP34" si="50">(AG11-AF11)/AF11</f>
+        <f t="shared" ref="AG34:AP34" si="52">(AG11-AF11)/AF11</f>
         <v>-1.0239037517809132E-2</v>
       </c>
       <c r="AH34" s="18">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0.10681225529083611</v>
       </c>
       <c r="AI34" s="18">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0.11951316449408197</v>
       </c>
       <c r="AJ34" s="18">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0.13999999999999982</v>
       </c>
       <c r="AK34" s="18">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0.13999999999999985</v>
       </c>
       <c r="AL34" s="18">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0.13999999999999985</v>
       </c>
       <c r="AM34" s="18">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0.13999999999999996</v>
       </c>
       <c r="AN34" s="18">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0.1399999999999999</v>
       </c>
       <c r="AO34" s="18">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0.13999999999999996</v>
       </c>
       <c r="AP34" s="18">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0.13999999999999993</v>
       </c>
       <c r="AR34" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AS34" s="44">
         <v>-0.01</v>
@@ -8571,50 +8846,50 @@
     </row>
     <row r="35" spans="2:45" x14ac:dyDescent="0.25">
       <c r="C35" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D35" s="20">
-        <f t="shared" ref="D35:N35" si="51">D13/D11</f>
+        <f t="shared" ref="D35:N35" si="53">D13/D11</f>
         <v>0.95828635851183763</v>
       </c>
       <c r="E35" s="20">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0.96443298969072166</v>
       </c>
       <c r="F35" s="20">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0.96671991480298192</v>
       </c>
       <c r="G35" s="20">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0.9651454363089268</v>
       </c>
       <c r="H35" s="20">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0.96705324196099107</v>
       </c>
       <c r="I35" s="20">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0.99063517915309451</v>
       </c>
       <c r="J35" s="20">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0.99025010597710894</v>
       </c>
       <c r="K35" s="20">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0.92641609317098994</v>
       </c>
       <c r="L35" s="20">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0.92849686847599167</v>
       </c>
       <c r="M35" s="20">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0.99207920792079207</v>
       </c>
       <c r="N35" s="20">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0.99271192942079023</v>
       </c>
       <c r="O35" s="20">
@@ -8626,50 +8901,56 @@
         <v>0.92208436724565757</v>
       </c>
       <c r="Q35" s="20">
-        <f t="shared" ref="Q35:S35" si="52">Q13/Q11</f>
+        <f t="shared" ref="Q35:S35" si="54">Q13/Q11</f>
         <v>0.91799410029498529</v>
       </c>
       <c r="R35" s="20">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0.90903387703889582</v>
       </c>
       <c r="S35" s="20">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0.89013898080741227</v>
       </c>
       <c r="T35" s="20">
-        <f t="shared" ref="T35:U35" si="53">T13/T11</f>
+        <f t="shared" ref="T35:U35" si="55">T13/T11</f>
         <v>0.91186001296176278</v>
       </c>
       <c r="U35" s="20">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0.91509433962264153</v>
       </c>
-      <c r="V35" s="20"/>
-      <c r="W35" s="20"/>
+      <c r="V35" s="20" t="e">
+        <f t="shared" ref="V35:W35" si="56">V13/V11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W35" s="20" t="e">
+        <f t="shared" si="56"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="X35" s="20"/>
       <c r="Z35" s="20">
-        <f t="shared" ref="Z35:AE35" si="54">Z13/Z11</f>
+        <f t="shared" ref="Z35:AE35" si="57">Z13/Z11</f>
         <v>0.96712242156010431</v>
       </c>
       <c r="AA35" s="20">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>0.96482801363495507</v>
       </c>
       <c r="AB35" s="20">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>0.96368734185871574</v>
       </c>
       <c r="AC35" s="20">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>0.96405185961236251</v>
       </c>
       <c r="AD35" s="20">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>0.93527635552054611</v>
       </c>
       <c r="AE35" s="20">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>0.92804804804804808</v>
       </c>
       <c r="AF35" s="20">
@@ -8677,47 +8958,47 @@
         <v>0.90580971980370428</v>
       </c>
       <c r="AG35" s="21">
-        <f t="shared" ref="AG35:AP35" si="55">AG13/AG11</f>
+        <f t="shared" ref="AG35:AP35" si="58">AG13/AG11</f>
         <v>0.90999999999999992</v>
       </c>
       <c r="AH35" s="20">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>0.91</v>
       </c>
       <c r="AI35" s="20">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>0.90999999999999992</v>
       </c>
       <c r="AJ35" s="20">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>0.91</v>
       </c>
       <c r="AK35" s="20">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>0.91</v>
       </c>
       <c r="AL35" s="20">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>0.90999999999999992</v>
       </c>
       <c r="AM35" s="20">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>0.91</v>
       </c>
       <c r="AN35" s="20">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>0.91</v>
       </c>
       <c r="AO35" s="20">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>0.91</v>
       </c>
       <c r="AP35" s="20">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>0.90999999999999992</v>
       </c>
       <c r="AR35" s="43" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AS35" s="45">
         <f>NPV(AS33,AF30:FC30)</f>
@@ -8729,103 +9010,109 @@
         <v>58</v>
       </c>
       <c r="D36" s="18">
-        <f t="shared" ref="D36:P36" si="56">D17/D11</f>
+        <f t="shared" ref="D36:P36" si="59">D17/D11</f>
         <v>0.10738444193912063</v>
       </c>
       <c r="E36" s="18">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>0.15953608247422679</v>
       </c>
       <c r="F36" s="18">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>0.17438764643237487</v>
       </c>
       <c r="G36" s="18">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>0.16298896690070211</v>
       </c>
       <c r="H36" s="18">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>0.11623616236162361</v>
       </c>
       <c r="I36" s="18">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>0.21905537459283386</v>
       </c>
       <c r="J36" s="18">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>0.24289953370072065</v>
       </c>
       <c r="K36" s="18">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>0.1725780836421387</v>
       </c>
       <c r="L36" s="18">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>0.17379958246346555</v>
       </c>
       <c r="M36" s="18">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>0.21623762376237624</v>
       </c>
       <c r="N36" s="18">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>0.25700038358266208</v>
       </c>
       <c r="O36" s="18">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>0.16017110266159695</v>
       </c>
       <c r="P36" s="18">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>0.19602977667493796</v>
       </c>
       <c r="Q36" s="18">
-        <f t="shared" ref="Q36:S36" si="57">Q17/Q11</f>
+        <f t="shared" ref="Q36:S36" si="60">Q17/Q11</f>
         <v>0.34513274336283184</v>
       </c>
       <c r="R36" s="18">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0.40087829360100374</v>
       </c>
       <c r="S36" s="18">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0.3256121773659828</v>
       </c>
       <c r="T36" s="18">
-        <f t="shared" ref="T36:U36" si="58">T17/T11</f>
+        <f t="shared" ref="T36:U36" si="61">T17/T11</f>
         <v>0.36422553467271551</v>
       </c>
       <c r="U36" s="18">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>0.39740566037735847</v>
       </c>
-      <c r="V36" s="18"/>
-      <c r="W36" s="18"/>
+      <c r="V36" s="18" t="e">
+        <f t="shared" ref="V36:W36" si="62">V17/V11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W36" s="18" t="e">
+        <f t="shared" si="62"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="X36" s="18"/>
       <c r="Y36" s="2"/>
       <c r="Z36" s="18">
-        <f t="shared" ref="Z36:AE36" si="59">Z17/Z11</f>
+        <f t="shared" ref="Z36:AE36" si="63">Z17/Z11</f>
         <v>0.15624753022998497</v>
       </c>
       <c r="AA36" s="18">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v>0.16478153083359157</v>
       </c>
       <c r="AB36" s="18">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v>0.18744443684606443</v>
       </c>
       <c r="AC36" s="18">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v>0.15760869565217392</v>
       </c>
       <c r="AD36" s="18">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v>0.20861231455953788</v>
       </c>
       <c r="AE36" s="18">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v>0.20384384384384385</v>
       </c>
       <c r="AF36" s="18">
@@ -8833,102 +9120,102 @@
         <v>0.33671046382776637</v>
       </c>
       <c r="AG36" s="19">
-        <f t="shared" ref="AG36:AP36" si="60">AG17/AG11</f>
+        <f t="shared" ref="AG36:AP36" si="64">AG17/AG11</f>
         <v>0.38676222586176007</v>
       </c>
       <c r="AH36" s="18">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>0.43016582919859309</v>
       </c>
       <c r="AI36" s="18">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>0.48139032749271121</v>
       </c>
       <c r="AJ36" s="18">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>0.53402660306378169</v>
       </c>
       <c r="AK36" s="18">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>0.54721865207908771</v>
       </c>
       <c r="AL36" s="18">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>0.55994782218157557</v>
       </c>
       <c r="AM36" s="18">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>0.57223035473660799</v>
       </c>
       <c r="AN36" s="18">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>0.58408192123707792</v>
       </c>
       <c r="AO36" s="18">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>0.59551764329893475</v>
       </c>
       <c r="AP36" s="18">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>0.60655211195511249</v>
       </c>
       <c r="AR36" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AS36" s="8">
-        <v>207.4</v>
+        <v>201.887</v>
       </c>
     </row>
     <row r="37" spans="2:45" x14ac:dyDescent="0.25">
       <c r="C37" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D37" s="20">
-        <f t="shared" ref="D37:O37" si="61">D22/D11</f>
+        <f t="shared" ref="D37:O37" si="65">D22/D11</f>
         <v>2.367531003382187E-2</v>
       </c>
       <c r="E37" s="20">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>7.422680412371134E-2</v>
       </c>
       <c r="F37" s="20">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>9.1054313099041537E-2</v>
       </c>
       <c r="G37" s="20">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>7.1213640922768301E-2</v>
       </c>
       <c r="H37" s="20">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>1.0015814443858724E-2</v>
       </c>
       <c r="I37" s="20">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>0.14535830618892509</v>
       </c>
       <c r="J37" s="20">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>0.16023738872403562</v>
       </c>
       <c r="K37" s="20">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>3.6527263102170464E-2</v>
       </c>
       <c r="L37" s="20">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>3.8100208768267224E-2</v>
       </c>
       <c r="M37" s="20">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>8.5940594059405934E-2</v>
       </c>
       <c r="N37" s="20">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>0.13195243574990412</v>
       </c>
       <c r="O37" s="20">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>-0.65826996197718635</v>
       </c>
       <c r="P37" s="20">
@@ -8936,34 +9223,40 @@
         <v>9.1811414392059559E-2</v>
       </c>
       <c r="Q37" s="20">
-        <f t="shared" ref="Q37:S37" si="62">Q22/Q11</f>
+        <f t="shared" ref="Q37:S37" si="66">Q22/Q11</f>
         <v>0.1952802359882006</v>
       </c>
       <c r="R37" s="20">
-        <f t="shared" si="62"/>
+        <f t="shared" si="66"/>
         <v>0.27540777917189463</v>
       </c>
       <c r="S37" s="20">
-        <f t="shared" si="62"/>
+        <f t="shared" si="66"/>
         <v>0.15552614162806089</v>
       </c>
       <c r="T37" s="20">
-        <f t="shared" ref="T37:U37" si="63">T22/T11</f>
+        <f t="shared" ref="T37:U37" si="67">T22/T11</f>
         <v>0.21386908619572262</v>
       </c>
       <c r="U37" s="20">
-        <f t="shared" si="63"/>
+        <f t="shared" si="67"/>
         <v>0.263561320754717</v>
       </c>
-      <c r="V37" s="20"/>
-      <c r="W37" s="20"/>
+      <c r="V37" s="20" t="e">
+        <f t="shared" ref="V37:W37" si="68">V22/V11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W37" s="20" t="e">
+        <f t="shared" si="68"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="X37" s="20"/>
       <c r="Z37" s="20">
-        <f t="shared" ref="Z37:AE37" si="64">Z22/Z11</f>
+        <f t="shared" ref="Z37:AE37" si="69">Z22/Z11</f>
         <v>7.2710029242076979E-2</v>
       </c>
       <c r="AA37" s="20">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>8.5373411837620081E-2</v>
       </c>
       <c r="AB37" s="20">
@@ -8971,15 +9264,15 @@
         <v>0.11263078711618683</v>
       </c>
       <c r="AC37" s="20">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>7.1961760083813511E-2</v>
       </c>
       <c r="AD37" s="20">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0.1165813312327688</v>
       </c>
       <c r="AE37" s="20">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>-0.10222222222222223</v>
       </c>
       <c r="AF37" s="20">
@@ -8987,51 +9280,51 @@
         <v>0.19423777109387366</v>
       </c>
       <c r="AG37" s="21">
-        <f t="shared" ref="AG37:AP37" si="65">AG22/AG11</f>
+        <f t="shared" ref="AG37:AP37" si="70">AG22/AG11</f>
         <v>0.24281565882744319</v>
       </c>
       <c r="AH37" s="20">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0.30011073959670559</v>
       </c>
       <c r="AI37" s="20">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0.35476381503886256</v>
       </c>
       <c r="AJ37" s="20">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0.41295388501580366</v>
       </c>
       <c r="AK37" s="20">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0.43145614096303841</v>
       </c>
       <c r="AL37" s="20">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0.44926261418465124</v>
       </c>
       <c r="AM37" s="20">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0.46639976112551379</v>
       </c>
       <c r="AN37" s="20">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0.48289302032822462</v>
       </c>
       <c r="AO37" s="20">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0.49876685207906613</v>
       </c>
       <c r="AP37" s="20">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0.51404477649050129</v>
       </c>
       <c r="AR37" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AS37" s="46">
         <f>AS35/AS36</f>
-        <v>280.2060099781084</v>
+        <v>287.85769499502044</v>
       </c>
     </row>
     <row r="38" spans="2:45" x14ac:dyDescent="0.25">
@@ -9074,79 +9367,85 @@
       <c r="AO38" s="20"/>
       <c r="AP38" s="20"/>
       <c r="AR38" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AS38" s="41">
         <f>(AS37-B4)/B4</f>
-        <v>0.17733617637860671</v>
+        <v>0.21458943035873604</v>
       </c>
     </row>
     <row r="39" spans="2:45" x14ac:dyDescent="0.25">
       <c r="C39" s="82" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D39" s="20"/>
       <c r="E39" s="20"/>
       <c r="F39" s="20"/>
       <c r="G39" s="20"/>
       <c r="H39" s="20">
-        <f t="shared" ref="H39:U42" si="66">(H4-D4)/D4</f>
+        <f t="shared" ref="H39:U42" si="71">(H4-D4)/D4</f>
         <v>0.13583138173302109</v>
       </c>
       <c r="I39" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0.21501014198782961</v>
       </c>
       <c r="J39" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0.14399999999999999</v>
       </c>
       <c r="K39" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0.15789473684210525</v>
       </c>
       <c r="L39" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0.13608247422680411</v>
       </c>
       <c r="M39" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>5.6761268781302172E-2</v>
       </c>
       <c r="N39" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>8.3916083916083919E-2</v>
       </c>
       <c r="O39" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>1.6363636363636365E-2</v>
       </c>
       <c r="P39" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>9.0744101633393835E-3</v>
       </c>
       <c r="Q39" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>6.7930489731437602E-2</v>
       </c>
       <c r="R39" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>9.3548387096774197E-2</v>
       </c>
       <c r="S39" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0.12164579606440072</v>
       </c>
       <c r="T39" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>3.0575539568345324E-2</v>
       </c>
       <c r="U39" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>8.8757396449704144E-3</v>
       </c>
-      <c r="V39" s="20"/>
-      <c r="W39" s="20"/>
+      <c r="V39" s="20">
+        <f t="shared" ref="V39:V42" si="72">(V4-R4)/R4</f>
+        <v>-1</v>
+      </c>
+      <c r="W39" s="20">
+        <f t="shared" ref="W39:W42" si="73">(W4-S4)/S4</f>
+        <v>-1</v>
+      </c>
       <c r="X39" s="20"/>
       <c r="Z39" s="20"/>
       <c r="AA39" s="20"/>
@@ -9155,112 +9454,118 @@
       <c r="AE39" s="20"/>
       <c r="AF39" s="20"/>
       <c r="AG39" s="21">
-        <f t="shared" ref="AG39:AP39" si="67">(AG4-AF4)/AF4</f>
+        <f t="shared" ref="AG39:AP39" si="74">(AG4-AF4)/AF4</f>
         <v>2.0000000000000094E-2</v>
       </c>
       <c r="AH39" s="20">
-        <f t="shared" si="67"/>
+        <f t="shared" si="74"/>
         <v>5.0000000000000058E-2</v>
       </c>
       <c r="AI39" s="20">
-        <f t="shared" si="67"/>
+        <f t="shared" si="74"/>
         <v>8.000000000000014E-2</v>
       </c>
       <c r="AJ39" s="20">
-        <f t="shared" si="67"/>
+        <f t="shared" si="74"/>
         <v>-1</v>
       </c>
       <c r="AK39" s="20" t="e">
-        <f t="shared" si="67"/>
+        <f t="shared" si="74"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL39" s="20" t="e">
-        <f t="shared" si="67"/>
+        <f t="shared" si="74"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AM39" s="20" t="e">
-        <f t="shared" si="67"/>
+        <f t="shared" si="74"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN39" s="20" t="e">
-        <f t="shared" si="67"/>
+        <f t="shared" si="74"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AO39" s="20" t="e">
-        <f t="shared" si="67"/>
+        <f t="shared" si="74"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP39" s="20" t="e">
-        <f t="shared" si="67"/>
+        <f t="shared" si="74"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="40" spans="2:45" x14ac:dyDescent="0.25">
       <c r="C40" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D40" s="20"/>
       <c r="E40" s="20"/>
       <c r="F40" s="20"/>
       <c r="G40" s="20"/>
       <c r="H40" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0.22033898305084745</v>
       </c>
       <c r="I40" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0.30530973451327431</v>
       </c>
       <c r="J40" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0.2669683257918552</v>
       </c>
       <c r="K40" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0.14563106796116504</v>
       </c>
       <c r="L40" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0.15740740740740741</v>
       </c>
       <c r="M40" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0.15593220338983052</v>
       </c>
       <c r="N40" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0.12857142857142856</v>
       </c>
       <c r="O40" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0.11440677966101695</v>
       </c>
       <c r="P40" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0.20399999999999999</v>
       </c>
       <c r="Q40" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0.11143695014662756</v>
       </c>
       <c r="R40" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>9.1772151898734181E-2</v>
       </c>
       <c r="S40" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0.14828897338403041</v>
       </c>
       <c r="T40" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0.13289036544850499</v>
       </c>
       <c r="U40" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0.13720316622691292</v>
       </c>
-      <c r="V40" s="20"/>
-      <c r="W40" s="20"/>
+      <c r="V40" s="20">
+        <f t="shared" si="72"/>
+        <v>-1</v>
+      </c>
+      <c r="W40" s="20">
+        <f t="shared" si="73"/>
+        <v>-1</v>
+      </c>
       <c r="X40" s="20"/>
       <c r="Z40" s="20"/>
       <c r="AA40" s="20"/>
@@ -9270,112 +9575,118 @@
       <c r="AE40" s="20"/>
       <c r="AF40" s="20"/>
       <c r="AG40" s="21">
-        <f t="shared" ref="AG40:AP40" si="68">(AG5-AF5)/AF5</f>
+        <f t="shared" ref="AG40:AP40" si="75">(AG5-AF5)/AF5</f>
         <v>0.12999999999999981</v>
       </c>
       <c r="AH40" s="20">
-        <f t="shared" si="68"/>
+        <f t="shared" si="75"/>
         <v>0.13999999999999982</v>
       </c>
       <c r="AI40" s="20">
-        <f t="shared" si="68"/>
+        <f t="shared" si="75"/>
         <v>0.13999999999999987</v>
       </c>
       <c r="AJ40" s="20">
-        <f t="shared" si="68"/>
+        <f t="shared" si="75"/>
         <v>-1</v>
       </c>
       <c r="AK40" s="20" t="e">
-        <f t="shared" si="68"/>
+        <f t="shared" si="75"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL40" s="20" t="e">
-        <f t="shared" si="68"/>
+        <f t="shared" si="75"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AM40" s="20" t="e">
-        <f t="shared" si="68"/>
+        <f t="shared" si="75"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN40" s="20" t="e">
-        <f t="shared" si="68"/>
+        <f t="shared" si="75"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AO40" s="20" t="e">
-        <f t="shared" si="68"/>
+        <f t="shared" si="75"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP40" s="20" t="e">
-        <f t="shared" si="68"/>
+        <f t="shared" si="75"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="41" spans="2:45" x14ac:dyDescent="0.25">
       <c r="C41" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D41" s="20"/>
       <c r="E41" s="20"/>
       <c r="F41" s="20"/>
       <c r="G41" s="20"/>
       <c r="H41" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>-5.5415617128463476E-2</v>
       </c>
       <c r="I41" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>-0.10354223433242507</v>
       </c>
       <c r="J41" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>-7.6923076923076927E-2</v>
       </c>
       <c r="K41" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>-8.6419753086419748E-2</v>
       </c>
       <c r="L41" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>-6.933333333333333E-2</v>
       </c>
       <c r="M41" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>-2.4316109422492401E-2</v>
       </c>
       <c r="N41" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>-2.4305555555555556E-2</v>
       </c>
       <c r="O41" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>-8.7837837837837843E-2</v>
       </c>
       <c r="P41" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>-0.10028653295128939</v>
       </c>
       <c r="Q41" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>-0.10903426791277258</v>
       </c>
       <c r="R41" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>-0.12099644128113879</v>
       </c>
       <c r="S41" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>3.7037037037037038E-3</v>
       </c>
       <c r="T41" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>8.2802547770700632E-2</v>
       </c>
       <c r="U41" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>5.2447552447552448E-2</v>
       </c>
-      <c r="V41" s="20"/>
-      <c r="W41" s="20"/>
+      <c r="V41" s="20">
+        <f t="shared" si="72"/>
+        <v>-1</v>
+      </c>
+      <c r="W41" s="20">
+        <f t="shared" si="73"/>
+        <v>-1</v>
+      </c>
       <c r="X41" s="20"/>
       <c r="Z41" s="20"/>
       <c r="AA41" s="20"/>
@@ -9385,112 +9696,118 @@
       <c r="AE41" s="20"/>
       <c r="AF41" s="20"/>
       <c r="AG41" s="21">
-        <f t="shared" ref="AG41:AP41" si="69">(AG6-AF6)/AF6</f>
+        <f t="shared" ref="AG41:AP41" si="76">(AG6-AF6)/AF6</f>
         <v>6.0000000000000137E-2</v>
       </c>
       <c r="AH41" s="20">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>0.10000000000000002</v>
       </c>
       <c r="AI41" s="20">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>0.10000000000000014</v>
       </c>
       <c r="AJ41" s="20">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>-1</v>
       </c>
       <c r="AK41" s="20" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL41" s="20" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AM41" s="20" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN41" s="20" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AO41" s="20" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP41" s="20" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="42" spans="2:45" x14ac:dyDescent="0.25">
       <c r="C42" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D42" s="20"/>
       <c r="E42" s="20"/>
       <c r="F42" s="20"/>
       <c r="G42" s="20"/>
       <c r="H42" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0.18320610687022901</v>
       </c>
       <c r="I42" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0.29104477611940299</v>
       </c>
       <c r="J42" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0.44</v>
       </c>
       <c r="K42" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0.31645569620253167</v>
       </c>
       <c r="L42" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0.22580645161290322</v>
       </c>
       <c r="M42" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0.16184971098265896</v>
       </c>
       <c r="N42" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0.16666666666666666</v>
       </c>
       <c r="O42" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>7.6923076923076927E-2</v>
       </c>
       <c r="P42" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>-5.2631578947368418E-2</v>
       </c>
       <c r="Q42" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>-4.4776119402985072E-2</v>
       </c>
       <c r="R42" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>-1.4285714285714285E-2</v>
       </c>
       <c r="S42" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>4.4642857142857144E-2</v>
       </c>
       <c r="T42" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0.2388888888888889</v>
       </c>
       <c r="U42" s="20">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0.234375</v>
       </c>
-      <c r="V42" s="20"/>
-      <c r="W42" s="20"/>
+      <c r="V42" s="20">
+        <f t="shared" si="72"/>
+        <v>-1</v>
+      </c>
+      <c r="W42" s="20">
+        <f t="shared" si="73"/>
+        <v>-1</v>
+      </c>
       <c r="X42" s="20"/>
       <c r="Z42" s="20"/>
       <c r="AA42" s="20"/>
@@ -9500,88 +9817,88 @@
       <c r="AE42" s="20"/>
       <c r="AF42" s="20"/>
       <c r="AG42" s="21">
-        <f t="shared" ref="AG42:AP42" si="70">(AG7-AF7)/AF7</f>
+        <f t="shared" ref="AG42:AP42" si="77">(AG7-AF7)/AF7</f>
         <v>0.23</v>
       </c>
       <c r="AH42" s="20">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>0.20000000000000004</v>
       </c>
       <c r="AI42" s="20">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>0.19999999999999993</v>
       </c>
       <c r="AJ42" s="20">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>-1</v>
       </c>
       <c r="AK42" s="20" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL42" s="20" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AM42" s="20" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN42" s="20" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AO42" s="20" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP42" s="20" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="43" spans="2:45" x14ac:dyDescent="0.25">
       <c r="C43" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D43" s="20"/>
       <c r="E43" s="20"/>
       <c r="F43" s="20"/>
       <c r="G43" s="20"/>
       <c r="H43" s="20">
-        <f t="shared" ref="H43:P43" si="71">(H8-D8)/D8</f>
+        <f t="shared" ref="H43:P43" si="78">(H8-D8)/D8</f>
         <v>-1.2578616352201259E-2</v>
       </c>
       <c r="I43" s="20">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>3.6319612590799029E-2</v>
       </c>
       <c r="J43" s="20">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>-3.5294117647058823E-2</v>
       </c>
       <c r="K43" s="20">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>-0.12450592885375494</v>
       </c>
       <c r="L43" s="20">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>-8.7048832271762203E-2</v>
       </c>
       <c r="M43" s="20">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>9.5794392523364483E-2</v>
       </c>
       <c r="N43" s="20">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>0.46097560975609758</v>
       </c>
       <c r="O43" s="20">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>0.41083521444695259</v>
       </c>
       <c r="P43" s="20">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>0.2441860465116279</v>
       </c>
       <c r="Q43" s="20"/>
@@ -9611,74 +9928,74 @@
     <row r="45" spans="2:45" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="21"/>
       <c r="C45" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D45" s="14">
-        <f t="shared" ref="D45:W45" si="72">SUM(D14:D16)</f>
+        <f t="shared" ref="D45:W45" si="79">SUM(D14:D16)</f>
         <v>-3019</v>
       </c>
       <c r="E45" s="14">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>-3123</v>
       </c>
       <c r="F45" s="14">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>-2976</v>
       </c>
       <c r="G45" s="14">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>-3199</v>
       </c>
       <c r="H45" s="14">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>-3228</v>
       </c>
       <c r="I45" s="14">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>-1895</v>
       </c>
       <c r="J45" s="14">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>-1763</v>
       </c>
       <c r="K45" s="14">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>-1424</v>
       </c>
       <c r="L45" s="14">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>-1446</v>
       </c>
       <c r="M45" s="14">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>-1959</v>
       </c>
       <c r="N45" s="14">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>-1918</v>
       </c>
       <c r="O45" s="14">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>-1594</v>
       </c>
       <c r="P45" s="14">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>-1463</v>
       </c>
       <c r="Q45" s="14">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>-971</v>
       </c>
       <c r="R45" s="14">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>-810</v>
       </c>
       <c r="S45" s="14">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>-853</v>
       </c>
       <c r="T45" s="14">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>-845</v>
       </c>
       <c r="U45" s="14">
@@ -9686,135 +10003,135 @@
         <v>-878</v>
       </c>
       <c r="V45" s="14">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="W45" s="14">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="X45" s="1"/>
       <c r="Y45" s="1"/>
       <c r="Z45" s="14">
-        <f t="shared" ref="Z45:AH45" si="73">SUM(Z14:Z16)</f>
+        <f t="shared" ref="Z45:AH45" si="80">SUM(Z14:Z16)</f>
         <v>-10260</v>
       </c>
       <c r="AA45" s="14">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>-10327</v>
       </c>
       <c r="AB45" s="14">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>-11351</v>
       </c>
       <c r="AC45" s="14">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>-12316</v>
       </c>
       <c r="AD45" s="14">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>-5535</v>
       </c>
       <c r="AE45" s="14">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>-6029</v>
       </c>
       <c r="AF45" s="14">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>-3595</v>
       </c>
       <c r="AG45" s="10">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>-3271.45</v>
       </c>
       <c r="AH45" s="14">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>-3320.5217499999999</v>
       </c>
       <c r="AI45" s="14">
-        <f t="shared" ref="AI45:AP45" si="74">SUM(AI14:AI16)</f>
+        <f t="shared" ref="AI45:AP45" si="81">SUM(AI14:AI16)</f>
         <v>-3320.5217499999999</v>
       </c>
       <c r="AJ45" s="14">
-        <f t="shared" si="74"/>
+        <f t="shared" si="81"/>
         <v>-3320.5217499999999</v>
       </c>
       <c r="AK45" s="14">
-        <f t="shared" si="74"/>
+        <f t="shared" si="81"/>
         <v>-3652.5739250000001</v>
       </c>
       <c r="AL45" s="14">
-        <f t="shared" si="74"/>
+        <f t="shared" si="81"/>
         <v>-4017.8313175000003</v>
       </c>
       <c r="AM45" s="14">
-        <f t="shared" si="74"/>
+        <f t="shared" si="81"/>
         <v>-4419.6144492500007</v>
       </c>
       <c r="AN45" s="14">
-        <f t="shared" si="74"/>
+        <f t="shared" si="81"/>
         <v>-4861.5758941750009</v>
       </c>
       <c r="AO45" s="14">
-        <f t="shared" si="74"/>
+        <f t="shared" si="81"/>
         <v>-5347.7334835925021</v>
       </c>
       <c r="AP45" s="14">
-        <f t="shared" si="74"/>
+        <f t="shared" si="81"/>
         <v>-5882.5068319517522</v>
       </c>
     </row>
     <row r="46" spans="2:45" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B46" s="21"/>
       <c r="C46" s="20" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H46" s="20">
-        <f t="shared" ref="H46:S46" si="75">(H45-D45)/D45</f>
+        <f t="shared" ref="H46:S46" si="82">(H45-D45)/D45</f>
         <v>6.9228221265319648E-2</v>
       </c>
       <c r="I46" s="20">
-        <f t="shared" si="75"/>
+        <f t="shared" si="82"/>
         <v>-0.3932116554594941</v>
       </c>
       <c r="J46" s="20">
-        <f t="shared" si="75"/>
+        <f t="shared" si="82"/>
         <v>-0.40759408602150538</v>
       </c>
       <c r="K46" s="20">
-        <f t="shared" si="75"/>
+        <f t="shared" si="82"/>
         <v>-0.55486089402938421</v>
       </c>
       <c r="L46" s="20">
-        <f t="shared" si="75"/>
+        <f t="shared" si="82"/>
         <v>-0.55204460966542745</v>
       </c>
       <c r="M46" s="20">
-        <f t="shared" si="75"/>
+        <f t="shared" si="82"/>
         <v>3.3773087071240104E-2</v>
       </c>
       <c r="N46" s="20">
-        <f t="shared" si="75"/>
+        <f t="shared" si="82"/>
         <v>8.7918321043675557E-2</v>
       </c>
       <c r="O46" s="20">
-        <f t="shared" si="75"/>
+        <f t="shared" si="82"/>
         <v>0.11938202247191011</v>
       </c>
       <c r="P46" s="20">
-        <f t="shared" si="75"/>
+        <f t="shared" si="82"/>
         <v>1.1756569847856155E-2</v>
       </c>
       <c r="Q46" s="20">
-        <f t="shared" si="75"/>
+        <f t="shared" si="82"/>
         <v>-0.50433894844308325</v>
       </c>
       <c r="R46" s="20">
-        <f t="shared" si="75"/>
+        <f t="shared" si="82"/>
         <v>-0.5776850886339937</v>
       </c>
       <c r="S46" s="20">
-        <f t="shared" si="75"/>
+        <f t="shared" si="82"/>
         <v>-0.46486825595984943</v>
       </c>
       <c r="T46" s="20">
@@ -9822,39 +10139,39 @@
         <v>-0.42241968557758031</v>
       </c>
       <c r="U46" s="20">
-        <f t="shared" ref="U46:W46" si="76">(U45-Q45)/Q45</f>
+        <f t="shared" ref="U46:W46" si="83">(U45-Q45)/Q45</f>
         <v>-9.577754891864057E-2</v>
       </c>
       <c r="V46" s="20">
-        <f t="shared" si="76"/>
+        <f t="shared" si="83"/>
         <v>-1</v>
       </c>
       <c r="W46" s="20">
-        <f t="shared" si="76"/>
+        <f t="shared" si="83"/>
         <v>-1</v>
       </c>
       <c r="AA46" s="20">
-        <f t="shared" ref="AA46:AF46" si="77">(AA45-Z45)/Z45</f>
+        <f t="shared" ref="AA46:AF46" si="84">(AA45-Z45)/Z45</f>
         <v>6.5302144249512672E-3</v>
       </c>
       <c r="AB46" s="20">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>9.9157548174687707E-2</v>
       </c>
       <c r="AC46" s="20">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>8.5014536164214602E-2</v>
       </c>
       <c r="AD46" s="20">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>-0.55058460539136078</v>
       </c>
       <c r="AE46" s="20">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>8.9250225835591696E-2</v>
       </c>
       <c r="AF46" s="20">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>-0.40371537568419308</v>
       </c>
       <c r="AG46" s="21">
@@ -9866,150 +10183,150 @@
         <v>1.500000000000002E-2</v>
       </c>
       <c r="AI46" s="20">
-        <f t="shared" ref="AI46:AP46" si="78">(AI45-AH45)/AH45</f>
+        <f t="shared" ref="AI46:AP46" si="85">(AI45-AH45)/AH45</f>
         <v>0</v>
       </c>
       <c r="AJ46" s="20">
-        <f t="shared" si="78"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="AK46" s="20">
-        <f t="shared" si="78"/>
+        <f t="shared" si="85"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AL46" s="20">
-        <f t="shared" si="78"/>
+        <f t="shared" si="85"/>
         <v>0.10000000000000003</v>
       </c>
       <c r="AM46" s="20">
-        <f t="shared" si="78"/>
+        <f t="shared" si="85"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AN46" s="20">
-        <f t="shared" si="78"/>
+        <f t="shared" si="85"/>
         <v>0.10000000000000005</v>
       </c>
       <c r="AO46" s="20">
-        <f t="shared" si="78"/>
+        <f t="shared" si="85"/>
         <v>0.10000000000000023</v>
       </c>
       <c r="AP46" s="20">
-        <f t="shared" si="78"/>
+        <f t="shared" si="85"/>
         <v>9.9999999999999978E-2</v>
       </c>
     </row>
     <row r="47" spans="2:45" x14ac:dyDescent="0.25">
       <c r="C47" s="20" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D47" s="20">
-        <f t="shared" ref="D47:W47" si="79">D45/D11</f>
+        <f t="shared" ref="D47:W47" si="86">D45/D11</f>
         <v>-0.85090191657271708</v>
       </c>
       <c r="E47" s="20">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>-0.80489690721649487</v>
       </c>
       <c r="F47" s="20">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>-0.792332268370607</v>
       </c>
       <c r="G47" s="20">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>-0.80215646940822471</v>
       </c>
       <c r="H47" s="20">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>-0.85081707959936748</v>
       </c>
       <c r="I47" s="20">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>-0.77157980456026054</v>
       </c>
       <c r="J47" s="20">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>-0.74735057227638835</v>
       </c>
       <c r="K47" s="20">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>-0.75383800952885127</v>
       </c>
       <c r="L47" s="20">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>-0.75469728601252606</v>
       </c>
       <c r="M47" s="20">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>-0.77584158415841586</v>
       </c>
       <c r="N47" s="20">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>-0.73571154583812814</v>
       </c>
       <c r="O47" s="20">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>-0.75760456273764254</v>
       </c>
       <c r="P47" s="20">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>-0.72605459057071964</v>
       </c>
       <c r="Q47" s="20">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>-0.57286135693215334</v>
       </c>
       <c r="R47" s="20">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>-0.50815558343789213</v>
       </c>
       <c r="S47" s="20">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>-0.56452680344142947</v>
       </c>
       <c r="T47" s="20">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>-0.54763447828904732</v>
       </c>
       <c r="U47" s="20">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>-0.51768867924528306</v>
       </c>
       <c r="V47" s="20" t="e">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W47" s="20" t="e">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X47" s="20"/>
       <c r="Y47" s="20"/>
       <c r="Z47" s="20">
-        <f t="shared" ref="Z47:AH47" si="80">Z45/Z11</f>
+        <f t="shared" ref="Z47:AH47" si="87">Z45/Z11</f>
         <v>-0.81087489133011936</v>
       </c>
       <c r="AA47" s="20">
-        <f t="shared" si="80"/>
+        <f t="shared" si="87"/>
         <v>-0.80004648280136348</v>
       </c>
       <c r="AB47" s="20">
-        <f t="shared" si="80"/>
+        <f t="shared" si="87"/>
         <v>-0.77624290501265125</v>
       </c>
       <c r="AC47" s="20">
-        <f t="shared" si="80"/>
+        <f t="shared" si="87"/>
         <v>-0.80644316396018856</v>
       </c>
       <c r="AD47" s="20">
-        <f t="shared" si="80"/>
+        <f t="shared" si="87"/>
         <v>-0.72666404096100823</v>
       </c>
       <c r="AE47" s="20">
-        <f t="shared" si="80"/>
+        <f t="shared" si="87"/>
         <v>-0.72420420420420417</v>
       </c>
       <c r="AF47" s="20">
-        <f t="shared" si="80"/>
+        <f t="shared" si="87"/>
         <v>-0.56909925597593791</v>
       </c>
       <c r="AG47" s="21">
@@ -10017,39 +10334,39 @@
         <v>-0.52323777413823991</v>
       </c>
       <c r="AH47" s="20">
-        <f t="shared" si="80"/>
+        <f t="shared" si="87"/>
         <v>-0.47983417080140695</v>
       </c>
       <c r="AI47" s="20">
-        <f t="shared" ref="AI47:AP47" si="81">AI45/AI11</f>
+        <f t="shared" ref="AI47:AP47" si="88">AI45/AI11</f>
         <v>-0.42860967250728876</v>
       </c>
       <c r="AJ47" s="20">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>-0.37597339693621823</v>
       </c>
       <c r="AK47" s="20">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>-0.36278134792091243</v>
       </c>
       <c r="AL47" s="20">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>-0.35005217781842435</v>
       </c>
       <c r="AM47" s="20">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>-0.33776964526339193</v>
       </c>
       <c r="AN47" s="20">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>-0.32591807876292206</v>
       </c>
       <c r="AO47" s="20">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>-0.31448235670106522</v>
       </c>
       <c r="AP47" s="20">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>-0.30344788804488754</v>
       </c>
     </row>
@@ -10983,47 +11300,47 @@
         <v>73</v>
       </c>
       <c r="D61" s="15">
-        <f t="shared" ref="D61:N61" si="82">SUM(D50:D60)</f>
+        <f t="shared" ref="D61:N61" si="89">SUM(D50:D60)</f>
         <v>50245</v>
       </c>
       <c r="E61" s="15">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>46421</v>
       </c>
       <c r="F61" s="15">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>44190</v>
       </c>
       <c r="G61" s="15">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>43709</v>
       </c>
       <c r="H61" s="15">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>46571</v>
       </c>
       <c r="I61" s="15">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>44247</v>
       </c>
       <c r="J61" s="15">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>56660</v>
       </c>
       <c r="K61" s="15">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>56237</v>
       </c>
       <c r="L61" s="15">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>56554</v>
       </c>
       <c r="M61" s="15">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>38881</v>
       </c>
       <c r="N61" s="15">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>41241</v>
       </c>
       <c r="O61" s="15">
@@ -11035,54 +11352,54 @@
         <v>36322</v>
       </c>
       <c r="Q61" s="15">
-        <f t="shared" ref="Q61:U61" si="83">SUM(Q50:Q60)</f>
+        <f t="shared" ref="Q61:U61" si="90">SUM(Q50:Q60)</f>
         <v>35217</v>
       </c>
       <c r="R61" s="15">
-        <f t="shared" si="83"/>
+        <f t="shared" si="90"/>
         <v>34420</v>
       </c>
       <c r="S61" s="15">
-        <f t="shared" si="83"/>
+        <f t="shared" si="90"/>
         <v>30884</v>
       </c>
       <c r="T61" s="15">
-        <f t="shared" si="83"/>
+        <f t="shared" si="90"/>
         <v>23873</v>
       </c>
       <c r="U61" s="15">
-        <f t="shared" si="83"/>
+        <f t="shared" si="90"/>
         <v>22434</v>
       </c>
       <c r="V61" s="15"/>
       <c r="W61" s="15"/>
       <c r="X61" s="15"/>
       <c r="Z61" s="15">
-        <f t="shared" ref="Z61:AF61" si="84">SUM(Z50:Z60)</f>
+        <f t="shared" ref="Z61:AF61" si="91">SUM(Z50:Z60)</f>
         <v>32778</v>
       </c>
       <c r="AA61" s="15">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>48477</v>
       </c>
       <c r="AB61" s="15">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>64189</v>
       </c>
       <c r="AC61" s="15">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>43757</v>
       </c>
       <c r="AD61" s="15">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>59237</v>
       </c>
       <c r="AE61" s="15">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>40098</v>
       </c>
       <c r="AF61" s="15">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>30884</v>
       </c>
     </row>
@@ -11337,47 +11654,47 @@
         <v>77</v>
       </c>
       <c r="D65" s="17">
-        <f t="shared" ref="D65:N65" si="85">SUM(D62:D64)</f>
+        <f t="shared" ref="D65:N65" si="92">SUM(D62:D64)</f>
         <v>35291</v>
       </c>
       <c r="E65" s="17">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>31159</v>
       </c>
       <c r="F65" s="17">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>28784</v>
       </c>
       <c r="G65" s="17">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>28666</v>
       </c>
       <c r="H65" s="17">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>31804</v>
       </c>
       <c r="I65" s="17">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>29476</v>
       </c>
       <c r="J65" s="17">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>42368</v>
       </c>
       <c r="K65" s="17">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>42426</v>
       </c>
       <c r="L65" s="17">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>43161</v>
       </c>
       <c r="M65" s="17">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>30427</v>
       </c>
       <c r="N65" s="17">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>33545</v>
       </c>
       <c r="O65" s="17">
@@ -11389,54 +11706,54 @@
         <v>28929</v>
       </c>
       <c r="Q65" s="17">
-        <f t="shared" ref="Q65:U65" si="86">SUM(Q62:Q64)</f>
+        <f t="shared" ref="Q65:U65" si="93">SUM(Q62:Q64)</f>
         <v>28082</v>
       </c>
       <c r="R65" s="17">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>27394</v>
       </c>
       <c r="S65" s="17">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>24537</v>
       </c>
       <c r="T65" s="17">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>17872</v>
       </c>
       <c r="U65" s="17">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>16437</v>
       </c>
       <c r="V65" s="17"/>
       <c r="W65" s="17"/>
       <c r="X65" s="17"/>
       <c r="Z65" s="17">
-        <f t="shared" ref="Z65:AF65" si="87">SUM(Z62:Z64)</f>
+        <f t="shared" ref="Z65:AF65" si="94">SUM(Z62:Z64)</f>
         <v>16881</v>
       </c>
       <c r="AA65" s="17">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>15854</v>
       </c>
       <c r="AB65" s="17">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>50532</v>
       </c>
       <c r="AC65" s="17">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>28666</v>
       </c>
       <c r="AD65" s="17">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>44603</v>
       </c>
       <c r="AE65" s="17">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>32504</v>
       </c>
       <c r="AF65" s="17">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>24537</v>
       </c>
     </row>
@@ -12347,47 +12664,47 @@
         <v>89</v>
       </c>
       <c r="D77" s="17">
-        <f t="shared" ref="D77:N77" si="88">SUM(D66:D76)</f>
+        <f t="shared" ref="D77:N77" si="95">SUM(D66:D76)</f>
         <v>14955</v>
       </c>
       <c r="E77" s="17">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>15262</v>
       </c>
       <c r="F77" s="17">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>15408</v>
       </c>
       <c r="G77" s="17">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>15042</v>
       </c>
       <c r="H77" s="17">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>14764</v>
       </c>
       <c r="I77" s="17">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>14769</v>
       </c>
       <c r="J77" s="17">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>14293</v>
       </c>
       <c r="K77" s="17">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>13810</v>
       </c>
       <c r="L77" s="17">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>13393</v>
       </c>
       <c r="M77" s="17">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>8452</v>
       </c>
       <c r="N77" s="17">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>7694</v>
       </c>
       <c r="O77" s="17">
@@ -12399,7 +12716,7 @@
         <v>7394</v>
       </c>
       <c r="Q77" s="17">
-        <f t="shared" ref="Q77:S77" si="89">SUM(Q66:Q76)</f>
+        <f t="shared" ref="Q77:S77" si="96">SUM(Q66:Q76)</f>
         <v>7133</v>
       </c>
       <c r="R77" s="17">
@@ -12407,46 +12724,46 @@
         <v>7025</v>
       </c>
       <c r="S77" s="17">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>6349</v>
       </c>
       <c r="T77" s="17">
-        <f t="shared" ref="T77:U77" si="90">SUM(T66:T76)</f>
+        <f t="shared" ref="T77:U77" si="97">SUM(T66:T76)</f>
         <v>6003</v>
       </c>
       <c r="U77" s="17">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>5995</v>
       </c>
       <c r="V77" s="17"/>
       <c r="W77" s="17"/>
       <c r="X77" s="17"/>
       <c r="Z77" s="17">
-        <f t="shared" ref="Z77:AF77" si="91">SUM(Z66:Z76)</f>
+        <f t="shared" ref="Z77:AF77" si="98">SUM(Z66:Z76)</f>
         <v>15897</v>
       </c>
       <c r="AA77" s="17">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>32624</v>
       </c>
       <c r="AB77" s="17">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>13656</v>
       </c>
       <c r="AC77" s="17">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>15042</v>
       </c>
       <c r="AD77" s="17">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>13810</v>
       </c>
       <c r="AE77" s="17">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>7593</v>
       </c>
       <c r="AF77" s="17">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>6349</v>
       </c>
     </row>
@@ -12455,47 +12772,47 @@
         <v>90</v>
       </c>
       <c r="D78" s="15">
-        <f t="shared" ref="D78:N78" si="92">D65+D77</f>
+        <f t="shared" ref="D78:N78" si="99">D65+D77</f>
         <v>50246</v>
       </c>
       <c r="E78" s="15">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>46421</v>
       </c>
       <c r="F78" s="15">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>44192</v>
       </c>
       <c r="G78" s="15">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>43708</v>
       </c>
       <c r="H78" s="15">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>46568</v>
       </c>
       <c r="I78" s="15">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>44245</v>
       </c>
       <c r="J78" s="15">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>56661</v>
       </c>
       <c r="K78" s="15">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>56236</v>
       </c>
       <c r="L78" s="15">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>56554</v>
       </c>
       <c r="M78" s="15">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>38879</v>
       </c>
       <c r="N78" s="15">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>41239</v>
       </c>
       <c r="O78" s="15">
@@ -12507,54 +12824,54 @@
         <v>36323</v>
       </c>
       <c r="Q78" s="15">
-        <f t="shared" ref="Q78:S78" si="93">Q65+Q77</f>
+        <f t="shared" ref="Q78:S78" si="100">Q65+Q77</f>
         <v>35215</v>
       </c>
       <c r="R78" s="15">
-        <f t="shared" si="93"/>
+        <f t="shared" si="100"/>
         <v>34419</v>
       </c>
       <c r="S78" s="15">
-        <f t="shared" si="93"/>
+        <f t="shared" si="100"/>
         <v>30886</v>
       </c>
       <c r="T78" s="15">
-        <f t="shared" ref="T78:U78" si="94">T65+T77</f>
+        <f t="shared" ref="T78:U78" si="101">T65+T77</f>
         <v>23875</v>
       </c>
       <c r="U78" s="15">
-        <f t="shared" si="94"/>
+        <f t="shared" si="101"/>
         <v>22432</v>
       </c>
       <c r="V78" s="15"/>
       <c r="W78" s="15"/>
       <c r="X78" s="15"/>
       <c r="Z78" s="15">
-        <f t="shared" ref="Z78:AF78" si="95">Z65+Z77</f>
+        <f t="shared" ref="Z78:AF78" si="102">Z65+Z77</f>
         <v>32778</v>
       </c>
       <c r="AA78" s="15">
-        <f t="shared" si="95"/>
+        <f t="shared" si="102"/>
         <v>48478</v>
       </c>
       <c r="AB78" s="15">
-        <f t="shared" si="95"/>
+        <f t="shared" si="102"/>
         <v>64188</v>
       </c>
       <c r="AC78" s="15">
-        <f t="shared" si="95"/>
+        <f t="shared" si="102"/>
         <v>43708</v>
       </c>
       <c r="AD78" s="15">
-        <f t="shared" si="95"/>
+        <f t="shared" si="102"/>
         <v>58413</v>
       </c>
       <c r="AE78" s="15">
-        <f t="shared" si="95"/>
+        <f t="shared" si="102"/>
         <v>40097</v>
       </c>
       <c r="AF78" s="15">
-        <f t="shared" si="95"/>
+        <f t="shared" si="102"/>
         <v>30886</v>
       </c>
     </row>
@@ -12566,7 +12883,7 @@
     </row>
     <row r="80" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C80" s="3" t="s">
-        <v>91</v>
+        <v>334</v>
       </c>
       <c r="O80" s="14"/>
       <c r="Q80" s="14"/>
@@ -12575,78 +12892,78 @@
     </row>
     <row r="81" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C81" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D81" s="14">
-        <f t="shared" ref="D81:U81" si="96">D28</f>
+        <f t="shared" ref="D81:U81" si="103">D28</f>
         <v>-13489</v>
       </c>
       <c r="E81" s="14">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>-6351</v>
       </c>
       <c r="F81" s="14">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>-3062</v>
       </c>
       <c r="G81" s="14">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>559</v>
       </c>
       <c r="H81" s="14">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>2197</v>
       </c>
       <c r="I81" s="14">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>3</v>
       </c>
       <c r="J81" s="14">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>1494</v>
       </c>
       <c r="K81" s="14">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>102</v>
       </c>
       <c r="L81" s="14">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>-83</v>
       </c>
       <c r="M81" s="14">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>185</v>
       </c>
       <c r="N81" s="14">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>5139</v>
       </c>
       <c r="O81" s="14">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>-349</v>
       </c>
       <c r="P81" s="14">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>-2262</v>
       </c>
       <c r="Q81" s="14">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>4912</v>
       </c>
       <c r="R81" s="14">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>-636</v>
       </c>
       <c r="S81" s="14">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>-2452</v>
       </c>
       <c r="T81" s="14">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>-5467</v>
       </c>
       <c r="U81" s="14">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>515</v>
       </c>
       <c r="V81" s="14"/>
@@ -12654,37 +12971,37 @@
       <c r="X81" s="14"/>
       <c r="Y81" s="14"/>
       <c r="Z81" s="14">
-        <f t="shared" ref="Z81:AF81" si="97">Z28</f>
+        <f t="shared" ref="Z81:AF81" si="104">Z28</f>
         <v>830</v>
       </c>
       <c r="AA81" s="14">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>942</v>
       </c>
       <c r="AB81" s="14">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>-18618</v>
       </c>
       <c r="AC81" s="14">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>-22244</v>
       </c>
       <c r="AD81" s="14">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>1839</v>
       </c>
       <c r="AE81" s="14">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>4800</v>
       </c>
       <c r="AF81" s="14">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>-396</v>
       </c>
     </row>
     <row r="82" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C82" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D82" s="14">
         <v>-13391</v>
@@ -12768,7 +13085,7 @@
     </row>
     <row r="83" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C83" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D83" s="14">
         <v>0</v>
@@ -12852,7 +13169,7 @@
     </row>
     <row r="84" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C84" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D84" s="14">
         <v>13796</v>
@@ -12936,7 +13253,7 @@
     </row>
     <row r="85" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C85" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D85" s="14">
         <v>55</v>
@@ -13020,7 +13337,7 @@
     </row>
     <row r="86" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C86" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D86" s="14">
         <v>-47</v>
@@ -13105,7 +13422,7 @@
     </row>
     <row r="87" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C87" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D87" s="14">
         <v>53</v>
@@ -13190,7 +13507,7 @@
     </row>
     <row r="88" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C88" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D88" s="14">
         <v>2</v>
@@ -13279,7 +13596,7 @@
     </row>
     <row r="89" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C89" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D89" s="14">
         <v>-46</v>
@@ -13363,7 +13680,7 @@
     </row>
     <row r="90" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C90" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D90" s="14">
         <v>-81</v>
@@ -13447,7 +13764,7 @@
     </row>
     <row r="91" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C91" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D91" s="14">
         <v>-64</v>
@@ -13531,7 +13848,7 @@
     </row>
     <row r="92" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C92" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D92" s="14">
         <v>-141</v>
@@ -13615,54 +13932,54 @@
     </row>
     <row r="93" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C93" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D93" s="15">
         <f>SUM(D82:D92)</f>
         <v>136</v>
       </c>
       <c r="E93" s="15">
-        <f t="shared" ref="E93:O93" si="98">SUM(E82:E92)</f>
+        <f t="shared" ref="E93:O93" si="105">SUM(E82:E92)</f>
         <v>398</v>
       </c>
       <c r="F93" s="15">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>433</v>
       </c>
       <c r="G93" s="15">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>714</v>
       </c>
       <c r="H93" s="15">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>216</v>
       </c>
       <c r="I93" s="15">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>442</v>
       </c>
       <c r="J93" s="15">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>527</v>
       </c>
       <c r="K93" s="15">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>522</v>
       </c>
       <c r="L93" s="15">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>108</v>
       </c>
       <c r="M93" s="15">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>234</v>
       </c>
       <c r="N93" s="15">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>724</v>
       </c>
       <c r="O93" s="15">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>375</v>
       </c>
       <c r="P93" s="15">
@@ -13670,23 +13987,23 @@
         <v>307</v>
       </c>
       <c r="Q93" s="15">
-        <f t="shared" ref="Q93:U93" si="99">SUM(Q82:Q92)</f>
+        <f t="shared" ref="Q93:U93" si="106">SUM(Q82:Q92)</f>
         <v>353</v>
       </c>
       <c r="R93" s="15">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>465</v>
       </c>
       <c r="S93" s="15">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>694</v>
       </c>
       <c r="T93" s="15">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>481</v>
       </c>
       <c r="U93" s="15">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>554</v>
       </c>
       <c r="V93" s="14"/>
@@ -13706,19 +14023,19 @@
         <v>2497</v>
       </c>
       <c r="AC93" s="15">
-        <f t="shared" ref="AC93:AF93" si="100">SUM(AC82:AC92)</f>
+        <f t="shared" ref="AC93:AF93" si="107">SUM(AC82:AC92)</f>
         <v>1685</v>
       </c>
       <c r="AD93" s="15">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>2362</v>
       </c>
       <c r="AE93" s="15">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>1440</v>
       </c>
       <c r="AF93" s="15">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>1814</v>
       </c>
     </row>
@@ -13755,7 +14072,7 @@
     </row>
     <row r="95" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C95" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D95" s="14">
         <f>-265-199-282</f>
@@ -13861,7 +14178,7 @@
     </row>
     <row r="96" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C96" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D96" s="14">
         <v>2</v>
@@ -13945,7 +14262,7 @@
     </row>
     <row r="97" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C97" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D97" s="14">
         <v>-1</v>
@@ -14029,7 +14346,7 @@
     </row>
     <row r="98" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C98" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D98" s="14">
         <v>0</v>
@@ -14113,7 +14430,7 @@
     </row>
     <row r="99" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C99" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D99" s="14">
         <v>0</v>
@@ -14197,7 +14514,7 @@
     </row>
     <row r="100" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C100" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D100" s="14">
         <v>0</v>
@@ -14282,54 +14599,54 @@
     </row>
     <row r="101" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C101" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D101" s="15">
-        <f t="shared" ref="D101:O101" si="101">SUM(D95:D100)</f>
+        <f t="shared" ref="D101:O101" si="108">SUM(D95:D100)</f>
         <v>-745</v>
       </c>
       <c r="E101" s="15">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>-359</v>
       </c>
       <c r="F101" s="15">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>-275</v>
       </c>
       <c r="G101" s="15">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>3994</v>
       </c>
       <c r="H101" s="15">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>-217</v>
       </c>
       <c r="I101" s="15">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>-509</v>
       </c>
       <c r="J101" s="15">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>-277</v>
       </c>
       <c r="K101" s="15">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>301</v>
       </c>
       <c r="L101" s="15">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>-499</v>
       </c>
       <c r="M101" s="15">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>28692</v>
       </c>
       <c r="N101" s="15">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>-266</v>
       </c>
       <c r="O101" s="15">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>-259</v>
       </c>
       <c r="P101" s="15">
@@ -14337,23 +14654,23 @@
         <v>-220</v>
       </c>
       <c r="Q101" s="15">
-        <f t="shared" ref="Q101:U101" si="102">SUM(Q95:Q100)</f>
+        <f t="shared" ref="Q101:U101" si="109">SUM(Q95:Q100)</f>
         <v>4100</v>
       </c>
       <c r="R101" s="15">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>-35</v>
       </c>
       <c r="S101" s="15">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>76</v>
       </c>
       <c r="T101" s="15">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>4160</v>
       </c>
       <c r="U101" s="15">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>-60</v>
       </c>
       <c r="V101" s="14"/>
@@ -14365,7 +14682,7 @@
         <v>-2245</v>
       </c>
       <c r="AA101" s="15">
-        <f t="shared" ref="AA101:AF101" si="103">SUM(AA95:AA100)</f>
+        <f t="shared" ref="AA101:AF101" si="110">SUM(AA95:AA100)</f>
         <v>-6108</v>
       </c>
       <c r="AB101" s="15">
@@ -14373,19 +14690,19 @@
         <v>-5923</v>
       </c>
       <c r="AC101" s="15">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>2615</v>
       </c>
       <c r="AD101" s="15">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>-700</v>
       </c>
       <c r="AE101" s="15">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>27217</v>
       </c>
       <c r="AF101" s="15">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>3921</v>
       </c>
     </row>
@@ -14422,7 +14739,7 @@
     </row>
     <row r="103" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C103" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D103" s="14">
         <v>1000</v>
@@ -14508,7 +14825,7 @@
     </row>
     <row r="104" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C104" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D104" s="14">
         <v>0</v>
@@ -14592,7 +14909,7 @@
     </row>
     <row r="105" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C105" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D105" s="14">
         <v>-87</v>
@@ -14676,7 +14993,7 @@
     </row>
     <row r="106" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C106" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D106" s="14">
         <v>-33</v>
@@ -14760,7 +15077,7 @@
     </row>
     <row r="107" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C107" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D107" s="14">
         <v>-33</v>
@@ -14844,7 +15161,7 @@
     </row>
     <row r="108" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C108" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D108" s="14">
         <v>0</v>
@@ -14928,7 +15245,7 @@
     </row>
     <row r="109" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C109" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D109" s="14">
         <v>0</v>
@@ -15012,7 +15329,7 @@
     </row>
     <row r="110" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C110" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D110" s="14">
         <v>0</v>
@@ -15096,54 +15413,54 @@
     </row>
     <row r="111" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C111" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D111" s="15">
-        <f t="shared" ref="D111:O111" si="104">SUM(D103:D110)</f>
+        <f t="shared" ref="D111:O111" si="111">SUM(D103:D110)</f>
         <v>847</v>
       </c>
       <c r="E111" s="15">
-        <f t="shared" si="104"/>
+        <f t="shared" si="111"/>
         <v>-1096</v>
       </c>
       <c r="F111" s="15">
-        <f t="shared" si="104"/>
+        <f t="shared" si="111"/>
         <v>-168</v>
       </c>
       <c r="G111" s="15">
-        <f t="shared" si="104"/>
+        <f t="shared" si="111"/>
         <v>-1256</v>
       </c>
       <c r="H111" s="15">
-        <f t="shared" si="104"/>
+        <f t="shared" si="111"/>
         <v>-1063</v>
       </c>
       <c r="I111" s="15">
-        <f t="shared" si="104"/>
+        <f t="shared" si="111"/>
         <v>-1131</v>
       </c>
       <c r="J111" s="15">
-        <f t="shared" si="104"/>
+        <f t="shared" si="111"/>
         <v>-631</v>
       </c>
       <c r="K111" s="15">
-        <f t="shared" si="104"/>
+        <f t="shared" si="111"/>
         <v>-650</v>
       </c>
       <c r="L111" s="15">
-        <f t="shared" si="104"/>
+        <f t="shared" si="111"/>
         <v>-627</v>
       </c>
       <c r="M111" s="15">
-        <f t="shared" si="104"/>
+        <f t="shared" si="111"/>
         <v>-19801</v>
       </c>
       <c r="N111" s="15">
-        <f t="shared" si="104"/>
+        <f t="shared" si="111"/>
         <v>-2987</v>
       </c>
       <c r="O111" s="15">
-        <f t="shared" si="104"/>
+        <f t="shared" si="111"/>
         <v>-958</v>
       </c>
       <c r="P111" s="15">
@@ -15151,23 +15468,23 @@
         <v>-1308</v>
       </c>
       <c r="Q111" s="15">
-        <f t="shared" ref="Q111:U111" si="105">SUM(Q103:Q110)</f>
+        <f t="shared" ref="Q111:U111" si="112">SUM(Q103:Q110)</f>
         <v>-6278</v>
       </c>
       <c r="R111" s="15">
-        <f t="shared" si="105"/>
+        <f t="shared" si="112"/>
         <v>-33</v>
       </c>
       <c r="S111" s="15">
-        <f t="shared" si="105"/>
+        <f t="shared" si="112"/>
         <v>-1216</v>
       </c>
       <c r="T111" s="15">
-        <f t="shared" si="105"/>
+        <f t="shared" si="112"/>
         <v>-1472</v>
       </c>
       <c r="U111" s="15">
-        <f t="shared" si="105"/>
+        <f t="shared" si="112"/>
         <v>-1902</v>
       </c>
       <c r="V111" s="14"/>
@@ -15179,7 +15496,7 @@
         <v>1429</v>
       </c>
       <c r="AA111" s="15">
-        <f t="shared" ref="AA111:AF111" si="106">SUM(AA103:AA110)</f>
+        <f t="shared" ref="AA111:AF111" si="113">SUM(AA103:AA110)</f>
         <v>2623</v>
       </c>
       <c r="AB111" s="15">
@@ -15187,19 +15504,19 @@
         <v>1910</v>
       </c>
       <c r="AC111" s="15">
-        <f t="shared" si="106"/>
+        <f t="shared" si="113"/>
         <v>-1672</v>
       </c>
       <c r="AD111" s="15">
-        <f t="shared" si="106"/>
+        <f t="shared" si="113"/>
         <v>-3474</v>
       </c>
       <c r="AE111" s="15">
-        <f t="shared" si="106"/>
+        <f t="shared" si="113"/>
         <v>-24374</v>
       </c>
       <c r="AF111" s="15">
-        <f t="shared" si="106"/>
+        <f t="shared" si="113"/>
         <v>-8833</v>
       </c>
     </row>
@@ -15236,7 +15553,7 @@
     </row>
     <row r="113" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C113" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D113" s="14">
         <v>-11</v>
@@ -15349,54 +15666,54 @@
     </row>
     <row r="115" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C115" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D115" s="14">
-        <f t="shared" ref="D115:O115" si="107">D93+D101+D111+D113</f>
+        <f t="shared" ref="D115:O115" si="114">D93+D101+D111+D113</f>
         <v>227</v>
       </c>
       <c r="E115" s="14">
-        <f t="shared" si="107"/>
+        <f t="shared" si="114"/>
         <v>-1044</v>
       </c>
       <c r="F115" s="14">
-        <f t="shared" si="107"/>
+        <f t="shared" si="114"/>
         <v>-9</v>
       </c>
       <c r="G115" s="14">
-        <f t="shared" si="107"/>
+        <f t="shared" si="114"/>
         <v>3450</v>
       </c>
       <c r="H115" s="14">
-        <f t="shared" si="107"/>
+        <f t="shared" si="114"/>
         <v>-1056</v>
       </c>
       <c r="I115" s="14">
-        <f t="shared" si="107"/>
+        <f t="shared" si="114"/>
         <v>-1198</v>
       </c>
       <c r="J115" s="14">
-        <f t="shared" si="107"/>
+        <f t="shared" si="114"/>
         <v>-384</v>
       </c>
       <c r="K115" s="14">
-        <f t="shared" si="107"/>
+        <f t="shared" si="114"/>
         <v>175</v>
       </c>
       <c r="L115" s="14">
-        <f t="shared" si="107"/>
+        <f t="shared" si="114"/>
         <v>-1017</v>
       </c>
       <c r="M115" s="14">
-        <f t="shared" si="107"/>
+        <f t="shared" si="114"/>
         <v>9123</v>
       </c>
       <c r="N115" s="14">
-        <f t="shared" si="107"/>
+        <f t="shared" si="114"/>
         <v>-2525</v>
       </c>
       <c r="O115" s="14">
-        <f t="shared" si="107"/>
+        <f t="shared" si="114"/>
         <v>-844</v>
       </c>
       <c r="P115" s="14">
@@ -15404,23 +15721,23 @@
         <v>-1220</v>
       </c>
       <c r="Q115" s="14">
-        <f t="shared" ref="Q115:S115" si="108">Q93+Q101+Q111+Q113</f>
+        <f t="shared" ref="Q115:S115" si="115">Q93+Q101+Q111+Q113</f>
         <v>-1824</v>
       </c>
       <c r="R115" s="14">
-        <f t="shared" si="108"/>
+        <f t="shared" si="115"/>
         <v>398</v>
       </c>
       <c r="S115" s="14">
-        <f t="shared" si="108"/>
+        <f t="shared" si="115"/>
         <v>-441</v>
       </c>
       <c r="T115" s="14">
-        <f t="shared" ref="T115:U115" si="109">T93+T101+T111+T113</f>
+        <f t="shared" ref="T115:U115" si="116">T93+T101+T111+T113</f>
         <v>3169</v>
       </c>
       <c r="U115" s="14">
-        <f t="shared" si="109"/>
+        <f t="shared" si="116"/>
         <v>-1409</v>
       </c>
       <c r="V115" s="14"/>
@@ -15432,7 +15749,7 @@
         <v>2021</v>
       </c>
       <c r="AA115" s="14">
-        <f t="shared" ref="AA115:AF115" si="110">AA93+AA101+AA111+AA113</f>
+        <f t="shared" ref="AA115:AF115" si="117">AA93+AA101+AA111+AA113</f>
         <v>-1189</v>
       </c>
       <c r="AB115" s="14">
@@ -15440,19 +15757,19 @@
         <v>-1570</v>
       </c>
       <c r="AC115" s="14">
-        <f t="shared" si="110"/>
+        <f t="shared" si="117"/>
         <v>2630</v>
       </c>
       <c r="AD115" s="14">
-        <f t="shared" si="110"/>
+        <f t="shared" si="117"/>
         <v>-1804</v>
       </c>
       <c r="AE115" s="14">
-        <f t="shared" si="110"/>
+        <f t="shared" si="117"/>
         <v>4284</v>
       </c>
       <c r="AF115" s="14">
-        <f t="shared" si="110"/>
+        <f t="shared" si="117"/>
         <v>-3090</v>
       </c>
     </row>
@@ -15489,54 +15806,54 @@
     </row>
     <row r="117" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C117" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D117" s="14">
-        <f t="shared" ref="D117:O117" si="111">D93+D95</f>
+        <f t="shared" ref="D117:O117" si="118">D93+D95</f>
         <v>-610</v>
       </c>
       <c r="E117" s="14">
-        <f t="shared" si="111"/>
+        <f t="shared" si="118"/>
         <v>44</v>
       </c>
       <c r="F117" s="14">
-        <f t="shared" si="111"/>
+        <f t="shared" si="118"/>
         <v>145</v>
       </c>
       <c r="G117" s="14">
-        <f t="shared" si="111"/>
+        <f t="shared" si="118"/>
         <v>165</v>
       </c>
       <c r="H117" s="14">
-        <f t="shared" si="111"/>
+        <f t="shared" si="118"/>
         <v>-19</v>
       </c>
       <c r="I117" s="14">
-        <f t="shared" si="111"/>
+        <f t="shared" si="118"/>
         <v>141</v>
       </c>
       <c r="J117" s="14">
-        <f t="shared" si="111"/>
+        <f t="shared" si="118"/>
         <v>289</v>
       </c>
       <c r="K117" s="14">
-        <f t="shared" si="111"/>
+        <f t="shared" si="118"/>
         <v>62</v>
       </c>
       <c r="L117" s="14">
-        <f t="shared" si="111"/>
+        <f t="shared" si="118"/>
         <v>-227</v>
       </c>
       <c r="M117" s="14">
-        <f t="shared" si="111"/>
+        <f t="shared" si="118"/>
         <v>399</v>
       </c>
       <c r="N117" s="14">
-        <f t="shared" si="111"/>
+        <f t="shared" si="118"/>
         <v>537</v>
       </c>
       <c r="O117" s="14">
-        <f t="shared" si="111"/>
+        <f t="shared" si="118"/>
         <v>152</v>
       </c>
       <c r="P117" s="14">
@@ -15544,23 +15861,23 @@
         <v>121</v>
       </c>
       <c r="Q117" s="14">
-        <f t="shared" ref="Q117:S117" si="112">Q93+Q95</f>
+        <f t="shared" ref="Q117:S117" si="119">Q93+Q95</f>
         <v>203</v>
       </c>
       <c r="R117" s="14">
-        <f t="shared" si="112"/>
+        <f t="shared" si="119"/>
         <v>336</v>
       </c>
       <c r="S117" s="14">
-        <f t="shared" si="112"/>
+        <f t="shared" si="119"/>
         <v>541</v>
       </c>
       <c r="T117" s="14">
-        <f t="shared" ref="T117:U117" si="113">T93+T95</f>
+        <f t="shared" ref="T117:U117" si="120">T93+T95</f>
         <v>280</v>
       </c>
       <c r="U117" s="14">
-        <f t="shared" si="113"/>
+        <f t="shared" si="120"/>
         <v>426</v>
       </c>
       <c r="V117" s="14"/>
@@ -15572,7 +15889,7 @@
         <v>1052</v>
       </c>
       <c r="AA117" s="14">
-        <f t="shared" ref="AA117:AF117" si="114">AA93+AA95</f>
+        <f t="shared" ref="AA117:AF117" si="121">AA93+AA95</f>
         <v>-693</v>
       </c>
       <c r="AB117" s="14">
@@ -15580,19 +15897,19 @@
         <v>-2128</v>
       </c>
       <c r="AC117" s="14">
-        <f t="shared" si="114"/>
+        <f t="shared" si="121"/>
         <v>-252</v>
       </c>
       <c r="AD117" s="14">
-        <f t="shared" si="114"/>
+        <f t="shared" si="121"/>
         <v>1128</v>
       </c>
       <c r="AE117" s="14">
-        <f t="shared" si="114"/>
+        <f t="shared" si="121"/>
         <v>408</v>
       </c>
       <c r="AF117" s="14">
-        <f t="shared" si="114"/>
+        <f t="shared" si="121"/>
         <v>1243</v>
       </c>
     </row>
@@ -15744,7 +16061,7 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -15755,121 +16072,121 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B5" s="48" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C5" s="48" t="s">
+        <v>321</v>
+      </c>
+      <c r="D5" s="48" t="s">
+        <v>181</v>
+      </c>
+      <c r="E5" s="48" t="s">
         <v>322</v>
       </c>
-      <c r="D5" s="48" t="s">
-        <v>182</v>
-      </c>
-      <c r="E5" s="48" t="s">
+      <c r="F5" s="48" t="s">
         <v>323</v>
-      </c>
-      <c r="F5" s="48" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B6" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="120">
+      <c r="C6" s="119">
         <v>1400</v>
       </c>
       <c r="D6" s="48">
         <v>18.5</v>
       </c>
-      <c r="E6" s="120">
+      <c r="E6" s="119">
         <f>D6*C6</f>
         <v>25900</v>
       </c>
-      <c r="F6" s="120">
+      <c r="F6" s="119">
         <f>E6/Modell!$B$5</f>
-        <v>121.59624413145539</v>
+        <v>128.28958773967616</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="120">
+      <c r="C7" s="119">
         <v>739</v>
       </c>
       <c r="D7" s="48">
         <v>18</v>
       </c>
-      <c r="E7" s="120">
+      <c r="E7" s="119">
         <f t="shared" ref="E7:E10" si="0">D7*C7</f>
         <v>13302</v>
       </c>
-      <c r="F7" s="120">
+      <c r="F7" s="119">
         <f>E7/Modell!$B$5</f>
-        <v>62.450704225352112</v>
+        <v>65.888343479273061</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B8" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="120">
+      <c r="C8" s="119">
         <v>740</v>
       </c>
       <c r="D8" s="48">
         <v>18</v>
       </c>
-      <c r="E8" s="120">
+      <c r="E8" s="119">
         <f t="shared" si="0"/>
         <v>13320</v>
       </c>
-      <c r="F8" s="120">
+      <c r="F8" s="119">
         <f>E8/Modell!$B$5</f>
-        <v>62.535211267605632</v>
+        <v>65.97750226611916</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="120">
+      <c r="C9" s="119">
         <v>-160</v>
       </c>
       <c r="D9" s="48">
         <v>5</v>
       </c>
-      <c r="E9" s="120">
+      <c r="E9" s="119">
         <f t="shared" si="0"/>
         <v>-800</v>
       </c>
-      <c r="F9" s="120">
+      <c r="F9" s="119">
         <f>E9/Modell!$B$5</f>
-        <v>-3.755868544600939</v>
+        <v>-3.9626127487158658</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B10" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="120">
+      <c r="C10" s="119">
         <v>-300</v>
       </c>
       <c r="D10" s="48">
         <v>11.4</v>
       </c>
-      <c r="E10" s="120">
+      <c r="E10" s="119">
         <f t="shared" si="0"/>
         <v>-3420</v>
       </c>
-      <c r="F10" s="120">
+      <c r="F10" s="119">
         <f>E10/Modell!$B$5</f>
-        <v>-16.056338028169016</v>
+        <v>-16.940169500760327</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B11" s="49" t="s">
-        <v>177</v>
-      </c>
-      <c r="C11" s="121">
+        <v>176</v>
+      </c>
+      <c r="C11" s="120">
         <f>SUM(C6:C10)</f>
         <v>2419</v>
       </c>
@@ -15877,127 +16194,127 @@
         <f>E11/C11</f>
         <v>19.967755270773047</v>
       </c>
-      <c r="E11" s="121">
+      <c r="E11" s="120">
         <f>SUM(E6:E10)</f>
         <v>48302</v>
       </c>
-      <c r="F11" s="121">
+      <c r="F11" s="120">
         <f>SUM(F6:F10)</f>
-        <v>226.76995305164317</v>
+        <v>239.2526512355922</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B12" s="51"/>
-      <c r="C12" s="122"/>
+      <c r="C12" s="121"/>
       <c r="D12" s="51"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="122"/>
+      <c r="E12" s="121"/>
+      <c r="F12" s="121"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B13" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="C13" s="120">
+        <v>177</v>
+      </c>
+      <c r="C13" s="119">
         <v>12000</v>
       </c>
       <c r="D13" s="48">
         <v>18.5</v>
       </c>
-      <c r="E13" s="120">
+      <c r="E13" s="119">
         <f>(C13*D13)*0.14</f>
         <v>31080.000000000004</v>
       </c>
-      <c r="F13" s="120">
+      <c r="F13" s="119">
         <f>E13/Modell!B5</f>
-        <v>145.91549295774649</v>
+        <v>153.94750528761139</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B14" s="48" t="s">
-        <v>325</v>
-      </c>
-      <c r="C14" s="120"/>
+        <v>324</v>
+      </c>
+      <c r="C14" s="119"/>
       <c r="D14" s="48"/>
-      <c r="E14" s="120">
+      <c r="E14" s="119">
         <v>-5000</v>
       </c>
-      <c r="F14" s="120">
+      <c r="F14" s="119">
         <f>E14/Modell!B5</f>
-        <v>-23.474178403755868</v>
+        <v>-24.766329679474161</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B15" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="C15" s="121"/>
+        <v>328</v>
+      </c>
+      <c r="C15" s="120"/>
       <c r="D15" s="49"/>
-      <c r="E15" s="121">
+      <c r="E15" s="120">
         <f>SUM(E13:E14)</f>
         <v>26080.000000000004</v>
       </c>
-      <c r="F15" s="121">
+      <c r="F15" s="120">
         <f>SUM(F13:F14)</f>
-        <v>122.44131455399062</v>
+        <v>129.18117560813724</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B16" s="51"/>
-      <c r="C16" s="122"/>
+      <c r="C16" s="121"/>
       <c r="D16" s="51"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="122"/>
+      <c r="E16" s="121"/>
+      <c r="F16" s="121"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="48" t="s">
-        <v>327</v>
-      </c>
-      <c r="C17" s="120"/>
+        <v>326</v>
+      </c>
+      <c r="C17" s="119"/>
       <c r="D17" s="48"/>
-      <c r="E17" s="120">
+      <c r="E17" s="119">
         <f>Modell!B7</f>
         <v>4222</v>
       </c>
-      <c r="F17" s="120">
+      <c r="F17" s="119">
         <f>E17/Modell!B5</f>
-        <v>19.821596244131456</v>
+        <v>20.912688781347981</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="48" t="s">
-        <v>326</v>
-      </c>
-      <c r="C18" s="120"/>
+        <v>325</v>
+      </c>
+      <c r="C18" s="119"/>
       <c r="D18" s="48"/>
-      <c r="E18" s="120">
+      <c r="E18" s="119">
         <f>Modell!B8</f>
         <v>2244</v>
       </c>
-      <c r="F18" s="120">
+      <c r="F18" s="119">
         <f>E18/(Modell!B5*-1)</f>
-        <v>-10.535211267605634</v>
+        <v>-11.115128760148004</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="51"/>
-      <c r="C19" s="122"/>
+      <c r="C19" s="121"/>
       <c r="D19" s="51"/>
-      <c r="E19" s="122"/>
-      <c r="F19" s="122"/>
+      <c r="E19" s="121"/>
+      <c r="F19" s="121"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="49" t="s">
-        <v>328</v>
-      </c>
-      <c r="C20" s="121"/>
+        <v>327</v>
+      </c>
+      <c r="C20" s="120"/>
       <c r="D20" s="49"/>
-      <c r="E20" s="121">
+      <c r="E20" s="120">
         <f>E11+E15+E17-E18</f>
         <v>76360</v>
       </c>
-      <c r="F20" s="121">
+      <c r="F20" s="120">
         <f>F11+F15+F17+F18</f>
-        <v>358.49765258215962</v>
+        <v>378.23138686492939</v>
       </c>
     </row>
     <row r="60" spans="2:2" x14ac:dyDescent="0.25">
@@ -16057,124 +16374,127 @@
       <c r="A87" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="B87" s="120">
+      <c r="B87" s="119">
         <f>F6</f>
-        <v>121.59624413145539</v>
+        <v>128.28958773967616</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="B88" s="120">
+      <c r="B88" s="119">
         <f t="shared" ref="B88:B101" si="1">F7</f>
-        <v>62.450704225352112</v>
+        <v>65.888343479273061</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="B89" s="120">
+      <c r="B89" s="119">
         <f t="shared" si="1"/>
-        <v>62.535211267605632</v>
+        <v>65.97750226611916</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="B90" s="120">
+      <c r="B90" s="119">
         <f t="shared" si="1"/>
-        <v>-3.755868544600939</v>
+        <v>-3.9626127487158658</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="B91" s="120">
+      <c r="B91" s="119">
         <f t="shared" si="1"/>
-        <v>-16.056338028169016</v>
+        <v>-16.940169500760327</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="49" t="s">
-        <v>177</v>
-      </c>
-      <c r="B92" s="120">
+        <v>176</v>
+      </c>
+      <c r="B92" s="119">
         <f t="shared" si="1"/>
-        <v>226.76995305164317</v>
+        <v>239.2526512355922</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="51"/>
-      <c r="B93" s="122"/>
+      <c r="B93" s="121"/>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="B94" s="120">
+        <v>177</v>
+      </c>
+      <c r="B94" s="119">
         <f t="shared" si="1"/>
-        <v>145.91549295774649</v>
+        <v>153.94750528761139</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="48" t="s">
-        <v>325</v>
-      </c>
-      <c r="B95" s="120">
+        <v>324</v>
+      </c>
+      <c r="B95" s="119">
         <f t="shared" si="1"/>
-        <v>-23.474178403755868</v>
+        <v>-24.766329679474161</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="B96" s="120">
+        <v>328</v>
+      </c>
+      <c r="B96" s="119">
         <f t="shared" si="1"/>
-        <v>122.44131455399062</v>
+        <v>129.18117560813724</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="51"/>
-      <c r="B97" s="122"/>
+      <c r="B97" s="121"/>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="48" t="s">
-        <v>327</v>
-      </c>
-      <c r="B98" s="120">
+        <v>326</v>
+      </c>
+      <c r="B98" s="119">
         <f t="shared" si="1"/>
-        <v>19.821596244131456</v>
+        <v>20.912688781347981</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="48" t="s">
-        <v>326</v>
-      </c>
-      <c r="B99" s="120">
+        <v>325</v>
+      </c>
+      <c r="B99" s="119">
         <f t="shared" si="1"/>
-        <v>-10.535211267605634</v>
+        <v>-11.115128760148004</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="51"/>
-      <c r="B100" s="122"/>
+      <c r="B100" s="121"/>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="49" t="s">
-        <v>328</v>
-      </c>
-      <c r="B101" s="120">
+        <v>327</v>
+      </c>
+      <c r="B101" s="119">
         <f t="shared" si="1"/>
-        <v>358.49765258215962</v>
+        <v>378.23138686492939</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="D11" formula="1"/>
+  </ignoredErrors>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
@@ -16202,7 +16522,7 @@
   <sheetData>
     <row r="4" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>6</v>
@@ -16250,31 +16570,31 @@
         <v>2024</v>
       </c>
       <c r="R4" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="S4" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="S4" s="13" t="s">
+      <c r="T4" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="T4" s="13" t="s">
+      <c r="U4" s="13" t="s">
         <v>100</v>
-      </c>
-      <c r="U4" s="13" t="s">
-        <v>101</v>
       </c>
       <c r="V4" s="28">
         <v>2025</v>
       </c>
       <c r="W4" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="X4" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="X4" s="13" t="s">
+      <c r="Y4" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="Y4" s="13" t="s">
+      <c r="Z4" s="13" t="s">
         <v>225</v>
-      </c>
-      <c r="Z4" s="13" t="s">
-        <v>226</v>
       </c>
       <c r="AA4" s="28">
         <v>2026</v>
@@ -16292,7 +16612,7 @@
     </row>
     <row r="6" spans="2:27" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C6" s="14">
         <f t="shared" ref="C6:Q6" si="0">SUM(C7:C8)</f>
@@ -16384,7 +16704,7 @@
     </row>
     <row r="7" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B7" s="30" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C7" s="31">
         <v>319</v>
@@ -16465,7 +16785,7 @@
     </row>
     <row r="8" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B8" s="30" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C8" s="31">
         <v>0</v>
@@ -16546,7 +16866,7 @@
     </row>
     <row r="9" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C9" s="1">
         <v>0</v>
@@ -16625,7 +16945,7 @@
     </row>
     <row r="10" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C10" s="1">
         <v>58</v>
@@ -16704,7 +17024,7 @@
     </row>
     <row r="11" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C11" s="1">
         <v>49</v>
@@ -16783,7 +17103,7 @@
     </row>
     <row r="12" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C12" s="15">
         <f t="shared" ref="C12:Q12" si="6">C6+C9+C10+C11</f>
@@ -16888,7 +17208,7 @@
     </row>
     <row r="13" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B13" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
@@ -16978,7 +17298,7 @@
     </row>
     <row r="14" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C14" s="15">
         <v>209</v>
@@ -17174,7 +17494,7 @@
     </row>
     <row r="17" spans="2:27" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C17" s="14">
         <f t="shared" ref="C17" si="19">SUM(C18:C19)</f>
@@ -17266,7 +17586,7 @@
     </row>
     <row r="18" spans="2:27" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="84" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C18" s="85">
         <v>147</v>
@@ -17347,7 +17667,7 @@
     </row>
     <row r="19" spans="2:27" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="84" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C19" s="85">
         <v>0</v>
@@ -17428,7 +17748,7 @@
     </row>
     <row r="20" spans="2:27" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C20" s="14">
         <v>0</v>
@@ -17507,7 +17827,7 @@
     </row>
     <row r="21" spans="2:27" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="14" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C21" s="14">
         <v>18</v>
@@ -17586,7 +17906,7 @@
     </row>
     <row r="22" spans="2:27" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="14" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C22" s="14">
         <v>11</v>
@@ -17665,7 +17985,7 @@
     </row>
     <row r="23" spans="2:27" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C23" s="15">
         <f t="shared" ref="C23" si="39">C17+C20+C21+C22</f>
@@ -17770,7 +18090,7 @@
     </row>
     <row r="24" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B24" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -17860,7 +18180,7 @@
     </row>
     <row r="25" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C25" s="2">
         <v>48</v>
@@ -18056,7 +18376,7 @@
     </row>
     <row r="28" spans="2:27" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C28" s="14">
         <f t="shared" ref="C28" si="82">SUM(C29:C30)</f>
@@ -18148,7 +18468,7 @@
     </row>
     <row r="29" spans="2:27" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="84" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C29" s="85">
         <v>392</v>
@@ -18229,7 +18549,7 @@
     </row>
     <row r="30" spans="2:27" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B30" s="84" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C30" s="85">
         <v>0</v>
@@ -18310,7 +18630,7 @@
     </row>
     <row r="31" spans="2:27" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C31" s="14">
         <v>0</v>
@@ -18389,7 +18709,7 @@
     </row>
     <row r="32" spans="2:27" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="14" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C32" s="14">
         <v>2</v>
@@ -18468,7 +18788,7 @@
     </row>
     <row r="33" spans="2:27" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="14" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C33" s="14">
         <v>3</v>
@@ -18547,7 +18867,7 @@
     </row>
     <row r="34" spans="2:27" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C34" s="15">
         <f t="shared" ref="C34" si="104">C28+C31+C32+C33</f>
@@ -18652,7 +18972,7 @@
     </row>
     <row r="35" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B35" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
@@ -18742,7 +19062,7 @@
     </row>
     <row r="36" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C36" s="2">
         <v>231</v>
@@ -18938,7 +19258,7 @@
     </row>
     <row r="39" spans="2:27" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B39" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C39" s="14">
         <f t="shared" ref="C39" si="149">SUM(C40:C41)</f>
@@ -19030,7 +19350,7 @@
     </row>
     <row r="40" spans="2:27" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="84" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C40" s="85">
         <v>75</v>
@@ -19111,7 +19431,7 @@
     </row>
     <row r="41" spans="2:27" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="84" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C41" s="85">
         <v>0</v>
@@ -19192,7 +19512,7 @@
     </row>
     <row r="42" spans="2:27" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B42" s="14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C42" s="14">
         <v>0</v>
@@ -19271,7 +19591,7 @@
     </row>
     <row r="43" spans="2:27" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B43" s="14" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C43" s="14">
         <v>50</v>
@@ -19350,7 +19670,7 @@
     </row>
     <row r="44" spans="2:27" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B44" s="14" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C44" s="14">
         <v>7</v>
@@ -19429,7 +19749,7 @@
     </row>
     <row r="45" spans="2:27" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C45" s="15">
         <f t="shared" ref="C45" si="171">C39+C42+C43+C44</f>
@@ -19534,7 +19854,7 @@
     </row>
     <row r="46" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B46" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C46" s="12"/>
       <c r="D46" s="12"/>
@@ -19624,7 +19944,7 @@
     </row>
     <row r="47" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B47" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C47" s="2">
         <v>-63</v>
@@ -19820,7 +20140,7 @@
     </row>
     <row r="50" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C50" s="1">
         <v>477</v>
@@ -19890,7 +20210,7 @@
     </row>
     <row r="51" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B51" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C51" s="1">
         <v>0</v>
@@ -19960,7 +20280,7 @@
     </row>
     <row r="52" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B52" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C52" s="2">
         <f t="shared" ref="C52" si="220">SUM(C50:C51)</f>
@@ -20047,7 +20367,7 @@
     </row>
     <row r="53" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G53" s="34"/>
       <c r="H53" s="38">
@@ -20118,7 +20438,7 @@
     </row>
     <row r="54" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B54" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C54" s="2">
         <v>-13</v>
@@ -20282,7 +20602,7 @@
     </row>
     <row r="56" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B56" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G56" s="33"/>
       <c r="L56" s="33"/>
@@ -20292,7 +20612,7 @@
     </row>
     <row r="57" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B57" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
@@ -20347,7 +20667,7 @@
     </row>
     <row r="58" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G58" s="26">
         <f>SUM(C58:F58)</f>
@@ -20390,7 +20710,7 @@
     </row>
     <row r="59" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B59" s="24" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C59" s="24"/>
       <c r="D59" s="24"/>
@@ -20526,7 +20846,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1322B806-2B16-F241-9CD3-A5DEE32230A2}">
-  <dimension ref="B4:X26"/>
+  <dimension ref="B4:X37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
@@ -20540,13 +20860,13 @@
   <sheetData>
     <row r="4" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>291</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>6</v>
@@ -20585,28 +20905,28 @@
         <v>17</v>
       </c>
       <c r="Q4" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="R4" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="R4" s="13" t="s">
+      <c r="S4" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="S4" s="13" t="s">
+      <c r="T4" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="T4" s="13" t="s">
-        <v>101</v>
-      </c>
       <c r="U4" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="V4" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="V4" s="13" t="s">
+      <c r="W4" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="W4" s="13" t="s">
+      <c r="X4" s="13" t="s">
         <v>225</v>
-      </c>
-      <c r="X4" s="13" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="5" spans="2:24" s="95" customFormat="1" x14ac:dyDescent="0.25">
@@ -20614,10 +20934,10 @@
         <v>52</v>
       </c>
       <c r="C5" s="95" t="s">
+        <v>291</v>
+      </c>
+      <c r="D5" s="95" t="s">
         <v>292</v>
-      </c>
-      <c r="D5" s="95" t="s">
-        <v>293</v>
       </c>
       <c r="M5" s="95">
         <v>438</v>
@@ -20653,7 +20973,7 @@
     <row r="6" spans="2:24" s="100" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="B6" s="99"/>
       <c r="D6" s="100" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q6" s="100">
         <f t="shared" ref="Q6:T6" si="0">(Q5-M5)/M5</f>
@@ -20682,10 +21002,10 @@
     </row>
     <row r="7" spans="2:24" s="95" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C7" s="95" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D7" s="95" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="M7" s="95">
         <v>622</v>
@@ -20720,7 +21040,7 @@
     </row>
     <row r="8" spans="2:24" s="101" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="D8" s="100" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E8" s="100"/>
       <c r="F8" s="100"/>
@@ -20763,10 +21083,10 @@
     </row>
     <row r="9" spans="2:24" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C9" s="96" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D9" s="96" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="M9" s="96">
         <v>309</v>
@@ -20801,7 +21121,7 @@
     </row>
     <row r="10" spans="2:24" s="101" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="D10" s="100" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E10" s="100"/>
       <c r="F10" s="100"/>
@@ -20844,10 +21164,10 @@
     </row>
     <row r="11" spans="2:24" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C11" s="96" t="s">
+        <v>293</v>
+      </c>
+      <c r="D11" s="96" t="s">
         <v>294</v>
-      </c>
-      <c r="D11" s="96" t="s">
-        <v>295</v>
       </c>
       <c r="M11" s="96">
         <v>171</v>
@@ -20882,7 +21202,7 @@
     </row>
     <row r="12" spans="2:24" s="101" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="D12" s="100" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E12" s="100"/>
       <c r="F12" s="100"/>
@@ -20925,10 +21245,10 @@
     </row>
     <row r="13" spans="2:24" s="97" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C13" s="97" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D13" s="97" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="M13" s="97">
         <v>4645</v>
@@ -20963,7 +21283,7 @@
     </row>
     <row r="14" spans="2:24" s="101" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="D14" s="100" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E14" s="100"/>
       <c r="F14" s="100"/>
@@ -21006,10 +21326,10 @@
     </row>
     <row r="15" spans="2:24" s="97" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C15" s="97" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D15" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="M15" s="97">
         <v>146</v>
@@ -21044,7 +21364,7 @@
     </row>
     <row r="16" spans="2:24" s="101" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="D16" s="100" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E16" s="100"/>
       <c r="F16" s="100"/>
@@ -21088,13 +21408,13 @@
     <row r="17" spans="2:22" s="68" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="18" spans="2:22" s="95" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="94" t="s">
+        <v>296</v>
+      </c>
+      <c r="C18" s="95" t="s">
+        <v>291</v>
+      </c>
+      <c r="D18" s="95" t="s">
         <v>297</v>
-      </c>
-      <c r="C18" s="95" t="s">
-        <v>292</v>
-      </c>
-      <c r="D18" s="95" t="s">
-        <v>298</v>
       </c>
       <c r="M18" s="95">
         <v>2925</v>
@@ -21130,7 +21450,7 @@
     <row r="19" spans="2:22" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="102"/>
       <c r="D19" s="100" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E19" s="100"/>
       <c r="F19" s="100"/>
@@ -21171,10 +21491,10 @@
     </row>
     <row r="20" spans="2:22" s="95" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C20" s="95" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D20" s="95" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="M20" s="95">
         <v>4645</v>
@@ -21209,7 +21529,7 @@
     </row>
     <row r="21" spans="2:22" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="100" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E21" s="100"/>
       <c r="F21" s="100"/>
@@ -21250,10 +21570,10 @@
     </row>
     <row r="22" spans="2:22" s="98" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C22" s="98" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D22" s="98" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="M22" s="98">
         <v>19</v>
@@ -21288,7 +21608,7 @@
     </row>
     <row r="23" spans="2:22" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="100" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E23" s="100"/>
       <c r="F23" s="100"/>
@@ -21333,10 +21653,10 @@
         <v>54</v>
       </c>
       <c r="C25" s="95" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D25" s="95" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="M25" s="95">
         <v>6685</v>
@@ -21371,7 +21691,7 @@
     </row>
     <row r="26" spans="2:22" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="100" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E26" s="100"/>
       <c r="F26" s="100"/>
@@ -21408,6 +21728,31 @@
       <c r="V26" s="100">
         <f>(V25-R25)/R25</f>
         <v>0.14886377445619151</v>
+      </c>
+    </row>
+    <row r="32" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B32" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="1" t="s">
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -21433,23 +21778,23 @@
   <sheetData>
     <row r="2" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3" spans="2:30" x14ac:dyDescent="0.25">
       <c r="AA3" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>291</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>6</v>
@@ -21488,40 +21833,40 @@
         <v>17</v>
       </c>
       <c r="Q4" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="R4" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="R4" s="13" t="s">
+      <c r="S4" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="S4" s="13" t="s">
+      <c r="T4" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="T4" s="13" t="s">
-        <v>101</v>
-      </c>
       <c r="U4" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="V4" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="V4" s="13" t="s">
+      <c r="W4" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="W4" s="13" t="s">
+      <c r="X4" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="X4" s="13" t="s">
-        <v>226</v>
-      </c>
       <c r="AA4" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="AB4" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="AB4" s="13" t="s">
+      <c r="AC4" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="AC4" s="13" t="s">
+      <c r="AD4" s="13" t="s">
         <v>305</v>
-      </c>
-      <c r="AD4" s="13" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="5" spans="2:30" x14ac:dyDescent="0.25">
@@ -21529,10 +21874,10 @@
         <v>52</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>292</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>293</v>
       </c>
       <c r="M5" s="1">
         <v>149</v>
@@ -21568,7 +21913,7 @@
     <row r="6" spans="2:30" s="100" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="B6" s="99"/>
       <c r="D6" s="100" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q6" s="100">
         <f t="shared" ref="Q6:T6" si="0">(Q5-M5)/M5</f>
@@ -21595,19 +21940,22 @@
         <v>4.6052631578947366E-2</v>
       </c>
       <c r="Z6" s="103"/>
-      <c r="AA6" s="100">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="100">
+      <c r="AA6" s="125">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="125">
         <v>0.03</v>
+      </c>
+      <c r="AC6" s="125">
+        <v>0.04</v>
       </c>
     </row>
     <row r="7" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C7" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="M7" s="1">
         <v>61</v>
@@ -21642,7 +21990,7 @@
     </row>
     <row r="8" spans="2:30" s="101" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="D8" s="100" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E8" s="100"/>
       <c r="F8" s="100"/>
@@ -21689,13 +22037,16 @@
       <c r="AB8" s="101">
         <v>-0.02</v>
       </c>
+      <c r="AC8" s="101">
+        <v>-0.02</v>
+      </c>
     </row>
     <row r="9" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C9" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="M9" s="1">
         <v>251</v>
@@ -21730,7 +22081,7 @@
     </row>
     <row r="10" spans="2:30" s="101" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="D10" s="100" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E10" s="100"/>
       <c r="F10" s="100"/>
@@ -21777,13 +22128,16 @@
       <c r="AB10" s="101">
         <v>-0.05</v>
       </c>
+      <c r="AC10" s="101">
+        <v>-0.02</v>
+      </c>
     </row>
     <row r="11" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C11" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>295</v>
       </c>
       <c r="M11" s="1">
         <v>165</v>
@@ -21818,7 +22172,7 @@
     </row>
     <row r="12" spans="2:30" s="101" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="D12" s="100" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E12" s="100"/>
       <c r="F12" s="100"/>
@@ -21865,13 +22219,16 @@
       <c r="AB12" s="101">
         <v>-0.13</v>
       </c>
+      <c r="AC12" s="101">
+        <v>-0.14000000000000001</v>
+      </c>
     </row>
     <row r="13" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C13" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="M13" s="1">
         <v>58</v>
@@ -21906,7 +22263,7 @@
     </row>
     <row r="14" spans="2:30" s="101" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="D14" s="100" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E14" s="100"/>
       <c r="F14" s="100"/>
@@ -21950,10 +22307,10 @@
     </row>
     <row r="15" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C15" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="M15" s="1">
         <v>51</v>
@@ -21988,7 +22345,7 @@
     </row>
     <row r="16" spans="2:30" s="101" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="D16" s="100" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E16" s="100"/>
       <c r="F16" s="100"/>
@@ -22035,19 +22392,22 @@
       <c r="AB16" s="101">
         <v>0.23</v>
       </c>
-    </row>
-    <row r="17" spans="2:28" s="68" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC16" s="101">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="17" spans="2:29" s="68" customFormat="1" x14ac:dyDescent="0.25">
       <c r="Z17" s="105"/>
     </row>
-    <row r="18" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>297</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>298</v>
       </c>
       <c r="M18" s="1">
         <v>51</v>
@@ -22080,10 +22440,10 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="2:28" s="44" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:29" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="102"/>
       <c r="D19" s="100" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E19" s="100"/>
       <c r="F19" s="100"/>
@@ -22128,13 +22488,16 @@
       <c r="AB19" s="44">
         <v>-0.03</v>
       </c>
-    </row>
-    <row r="20" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="AC19" s="44">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="20" spans="2:29" x14ac:dyDescent="0.25">
       <c r="C20" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="M20" s="1">
         <v>23</v>
@@ -22167,9 +22530,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="2:28" s="44" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:29" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="100" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E21" s="100"/>
       <c r="F21" s="100"/>
@@ -22214,13 +22577,16 @@
       <c r="AB21" s="44">
         <v>-0.02</v>
       </c>
-    </row>
-    <row r="22" spans="2:28" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC21" s="44">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="22" spans="2:29" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C22" s="14" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="M22" s="14">
         <v>104</v>
@@ -22254,9 +22620,9 @@
       </c>
       <c r="Z22" s="10"/>
     </row>
-    <row r="23" spans="2:28" s="44" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:29" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="100" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E23" s="100"/>
       <c r="F23" s="100"/>
@@ -22296,18 +22662,18 @@
       </c>
       <c r="Z23" s="106"/>
     </row>
-    <row r="24" spans="2:28" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:29" s="68" customFormat="1" x14ac:dyDescent="0.25">
       <c r="Z24" s="105"/>
     </row>
-    <row r="25" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="M25" s="1">
         <v>44</v>
@@ -22340,9 +22706,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="2:28" s="44" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:29" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="100" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E26" s="100"/>
       <c r="F26" s="100"/>
@@ -22386,6 +22752,9 @@
       </c>
       <c r="AB26" s="44">
         <v>-0.13</v>
+      </c>
+      <c r="AC26" s="44">
+        <v>-0.04</v>
       </c>
     </row>
   </sheetData>
@@ -22407,28 +22776,28 @@
   <sheetData>
     <row r="2" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.2">
       <c r="Z4" s="110" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="19" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>291</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>6</v>
@@ -22467,40 +22836,40 @@
         <v>17</v>
       </c>
       <c r="Q5" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="R5" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="R5" s="13" t="s">
+      <c r="S5" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="S5" s="13" t="s">
+      <c r="T5" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="T5" s="13" t="s">
-        <v>101</v>
-      </c>
       <c r="U5" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="V5" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="V5" s="13" t="s">
+      <c r="W5" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="W5" s="13" t="s">
+      <c r="X5" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="X5" s="13" t="s">
-        <v>226</v>
-      </c>
       <c r="Z5" s="111" t="s">
+        <v>302</v>
+      </c>
+      <c r="AA5" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="AA5" s="13" t="s">
+      <c r="AB5" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="AB5" s="13" t="s">
+      <c r="AC5" s="13" t="s">
         <v>305</v>
-      </c>
-      <c r="AC5" s="13" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="6" spans="1:29" s="95" customFormat="1" ht="19" x14ac:dyDescent="0.25">
@@ -22508,10 +22877,10 @@
         <v>55</v>
       </c>
       <c r="C6" s="95" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D6" s="95" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="O6" s="95">
         <v>481</v>
@@ -22543,7 +22912,7 @@
       <c r="B7" s="99"/>
       <c r="C7" s="100"/>
       <c r="D7" s="100" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="S7" s="101">
         <f>(S6-O6)/O6</f>
@@ -22567,13 +22936,16 @@
       <c r="AA7" s="101">
         <v>0.18</v>
       </c>
+      <c r="AB7" s="101">
+        <v>0.21</v>
+      </c>
     </row>
     <row r="8" spans="1:29" s="44" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="C8" s="44" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D8" s="44" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O8" s="44">
         <v>0.16</v>
@@ -22604,10 +22976,10 @@
     <row r="9" spans="1:29" s="108" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="B9" s="96"/>
       <c r="C9" s="96" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D9" s="96" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="O9" s="108">
         <v>173</v>
@@ -22637,7 +23009,7 @@
     </row>
     <row r="10" spans="1:29" s="101" customFormat="1" x14ac:dyDescent="0.2">
       <c r="D10" s="100" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="S10" s="101">
         <f>(S9-O9)/O9</f>
@@ -22661,13 +23033,16 @@
       <c r="AA10" s="101">
         <v>0</v>
       </c>
+      <c r="AB10" s="101">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="11" spans="1:29" s="44" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="C11" s="44" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O11" s="44">
         <v>0.1</v>
@@ -22698,10 +23073,10 @@
     <row r="12" spans="1:29" s="109" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="B12" s="98"/>
       <c r="C12" s="98" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D12" s="98" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="O12" s="109">
         <v>8</v>
@@ -22731,7 +23106,7 @@
     </row>
     <row r="13" spans="1:29" s="101" customFormat="1" x14ac:dyDescent="0.2">
       <c r="D13" s="100" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="S13" s="101">
         <f>(S12-O12)/O12</f>
@@ -22755,13 +23130,16 @@
       <c r="AA13" s="101">
         <v>0.35</v>
       </c>
+      <c r="AB13" s="101">
+        <v>0.31</v>
+      </c>
     </row>
     <row r="14" spans="1:29" s="44" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="C14" s="44" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O14" s="44">
         <v>0.15</v>
@@ -22791,10 +23169,10 @@
     </row>
     <row r="15" spans="1:29" s="97" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="C15" s="97" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D15" s="97" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q15" s="97">
         <v>16</v>
@@ -22818,7 +23196,7 @@
     </row>
     <row r="16" spans="1:29" s="101" customFormat="1" x14ac:dyDescent="0.2">
       <c r="D16" s="101" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="U16" s="101">
         <f>(U15-Q15)/Q15</f>
@@ -22832,13 +23210,16 @@
       <c r="AA16" s="101">
         <v>0.73</v>
       </c>
+      <c r="AB16" s="101">
+        <v>0.47</v>
+      </c>
     </row>
     <row r="17" spans="3:26" s="44" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="C17" s="44" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D17" s="44" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q17" s="44">
         <v>0.14000000000000001</v>
@@ -22892,53 +23273,53 @@
     </row>
     <row r="5" spans="3:6" ht="62" x14ac:dyDescent="0.7">
       <c r="C5" s="16" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D5" s="42">
         <f>Modell!$B$9/Modell!AG17</f>
-        <v>20.145886055900661</v>
+        <v>18.968635755134937</v>
       </c>
       <c r="E5" s="56">
         <f>Modell!$B$9/Modell!AH17</f>
-        <v>16.365171328485616</v>
+        <v>15.408851868766476</v>
       </c>
       <c r="F5" s="59">
         <f>Modell!$B$9/Modell!AI17</f>
-        <v>13.062608185053376</v>
+        <v>12.299278174550574</v>
       </c>
     </row>
     <row r="6" spans="3:6" ht="62" x14ac:dyDescent="0.7">
       <c r="C6" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D6" s="42">
         <f>Modell!$B$9/Modell!AG22</f>
-        <v>32.088819026596134</v>
+        <v>30.21366835089713</v>
       </c>
       <c r="E6" s="56">
         <f>Modell!$B$9/Modell!AH22</f>
-        <v>23.457132870203804</v>
+        <v>22.08638567894484</v>
       </c>
       <c r="F6" s="59">
         <f>Modell!$B$9/Modell!AI22</f>
-        <v>17.725069371640885</v>
+        <v>16.689282551892358</v>
       </c>
     </row>
     <row r="7" spans="3:6" ht="62" x14ac:dyDescent="0.7">
       <c r="C7" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D7" s="42">
         <f>Modell!$B$4/Modell!AG31</f>
-        <v>41.684367736173051</v>
+        <v>40.40584653430642</v>
       </c>
       <c r="E7" s="56">
         <f>Modell!$B$4/Modell!AH31</f>
-        <v>30.471540625643552</v>
+        <v>29.536933412934939</v>
       </c>
       <c r="F7" s="58">
         <f>Modell!$B$4/Modell!AI31</f>
-        <v>23.025412970925153</v>
+        <v>22.319189504819501</v>
       </c>
     </row>
   </sheetData>
@@ -22962,7 +23343,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="60" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -22984,7 +23365,7 @@
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B3"/>
       <c r="C3"/>
@@ -23008,7 +23389,7 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B4" s="61">
         <f>Modell!AH17</f>
@@ -23035,10 +23416,10 @@
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B5" s="8">
-        <v>207.4</v>
+        <v>201.887</v>
       </c>
       <c r="C5"/>
       <c r="D5"/>
@@ -23061,11 +23442,11 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B6" s="61">
         <f>Modell!B9</f>
-        <v>48716</v>
+        <v>45869.218999999997</v>
       </c>
       <c r="C6"/>
       <c r="D6"/>
@@ -23110,16 +23491,16 @@
     </row>
     <row r="8" spans="1:20" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="73" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B8" s="62" t="s">
+        <v>236</v>
+      </c>
+      <c r="C8" s="62" t="s">
         <v>237</v>
       </c>
-      <c r="C8" s="62" t="s">
+      <c r="D8" s="88" t="s">
         <v>238</v>
-      </c>
-      <c r="D8" s="88" t="s">
-        <v>239</v>
       </c>
       <c r="E8"/>
       <c r="F8"/>
@@ -23139,7 +23520,7 @@
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="74" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B9" s="75">
         <f>$B$4*10</f>
@@ -23147,11 +23528,11 @@
       </c>
       <c r="C9" s="75">
         <f t="shared" ref="C9:C29" si="0">B9/$B$5</f>
-        <v>143.52987724204439</v>
+        <v>147.44929856801085</v>
       </c>
       <c r="D9" s="89">
         <f>B9/$B$6-1</f>
-        <v>-0.38894620781673361</v>
+        <v>-0.3510223808257994</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -23171,7 +23552,7 @@
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="76" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B10" s="77">
         <f>$B$4*11</f>
@@ -23179,11 +23560,11 @@
       </c>
       <c r="C10" s="77">
         <f t="shared" si="0"/>
-        <v>157.88286496624883</v>
+        <v>162.19422842481194</v>
       </c>
       <c r="D10" s="90">
         <f t="shared" ref="D10:D29" si="1">B10/$B$6-1</f>
-        <v>-0.32784082859840691</v>
+        <v>-0.28612461890837926</v>
       </c>
       <c r="E10"/>
       <c r="F10"/>
@@ -23203,7 +23584,7 @@
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="76" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B11" s="77">
         <f>$B$4*12</f>
@@ -23211,11 +23592,11 @@
       </c>
       <c r="C11" s="77">
         <f t="shared" si="0"/>
-        <v>172.23585269045327</v>
+        <v>176.939158281613</v>
       </c>
       <c r="D11" s="90">
         <f t="shared" si="1"/>
-        <v>-0.26673544938008031</v>
+        <v>-0.22122685699095923</v>
       </c>
       <c r="E11"/>
       <c r="F11"/>
@@ -23235,7 +23616,7 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="76" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B12" s="77">
         <f>$B$4*13</f>
@@ -23243,11 +23624,11 @@
       </c>
       <c r="C12" s="77">
         <f t="shared" si="0"/>
-        <v>186.58884041465768</v>
+        <v>191.6840881384141</v>
       </c>
       <c r="D12" s="90">
         <f t="shared" si="1"/>
-        <v>-0.20563007016175372</v>
+        <v>-0.15632909507353931</v>
       </c>
       <c r="E12"/>
       <c r="F12"/>
@@ -23267,7 +23648,7 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="76" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B13" s="77">
         <f>$B$4*14</f>
@@ -23275,11 +23656,11 @@
       </c>
       <c r="C13" s="77">
         <f t="shared" si="0"/>
-        <v>200.94182813886215</v>
+        <v>206.42901799521519</v>
       </c>
       <c r="D13" s="90">
         <f t="shared" si="1"/>
-        <v>-0.14452469094342701</v>
+        <v>-9.1431333156119177E-2</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -23299,7 +23680,7 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="76" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B14" s="77">
         <f>$B$4*15</f>
@@ -23307,11 +23688,11 @@
       </c>
       <c r="C14" s="77">
         <f t="shared" si="0"/>
-        <v>215.29481586306659</v>
+        <v>221.17394785201628</v>
       </c>
       <c r="D14" s="90">
         <f t="shared" si="1"/>
-        <v>-8.3419311725100309E-2</v>
+        <v>-2.6533571238698928E-2</v>
       </c>
       <c r="E14"/>
       <c r="F14"/>
@@ -23331,7 +23712,7 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="76" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B15" s="77">
         <f>$B$4*16</f>
@@ -23339,11 +23720,11 @@
       </c>
       <c r="C15" s="77">
         <f t="shared" si="0"/>
-        <v>229.647803587271</v>
+        <v>235.91887770881735</v>
       </c>
       <c r="D15" s="90">
         <f>B15/$B$6-1</f>
-        <v>-2.2313932506773715E-2</v>
+        <v>3.83641906787211E-2</v>
       </c>
       <c r="E15"/>
       <c r="F15"/>
@@ -23363,7 +23744,7 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="76" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B16" s="77">
         <f>$B$4*17</f>
@@ -23371,11 +23752,11 @@
       </c>
       <c r="C16" s="77">
         <f t="shared" si="0"/>
-        <v>244.00079131147544</v>
+        <v>250.66380756561841</v>
       </c>
       <c r="D16" s="90">
         <f t="shared" si="1"/>
-        <v>3.8791446711552879E-2</v>
+        <v>0.1032619525961409</v>
       </c>
       <c r="E16"/>
       <c r="F16"/>
@@ -23395,7 +23776,7 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="76" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B17" s="77">
         <f>$B$4*18</f>
@@ -23403,11 +23784,11 @@
       </c>
       <c r="C17" s="77">
         <f t="shared" si="0"/>
-        <v>258.35377903567991</v>
+        <v>265.40873742241951</v>
       </c>
       <c r="D17" s="90">
         <f t="shared" si="1"/>
-        <v>9.9896825929879585E-2</v>
+        <v>0.16815971451356115</v>
       </c>
       <c r="E17"/>
       <c r="F17"/>
@@ -23427,7 +23808,7 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="76" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B18" s="77">
         <f>$B$4*19</f>
@@ -23435,11 +23816,11 @@
       </c>
       <c r="C18" s="77">
         <f t="shared" si="0"/>
-        <v>272.70676675988437</v>
+        <v>280.1536672792206</v>
       </c>
       <c r="D18" s="90">
         <f t="shared" si="1"/>
-        <v>0.16100220514820629</v>
+        <v>0.23305747643098118</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -23459,7 +23840,7 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="78" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B19" s="79">
         <f>$B$4*20</f>
@@ -23467,11 +23848,11 @@
       </c>
       <c r="C19" s="79">
         <f t="shared" si="0"/>
-        <v>287.05975448408878</v>
+        <v>294.89859713602169</v>
       </c>
       <c r="D19" s="91">
         <f t="shared" si="1"/>
-        <v>0.22210758436653277</v>
+        <v>0.29795523834840121</v>
       </c>
       <c r="E19"/>
       <c r="F19"/>
@@ -23491,7 +23872,7 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="76" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B20" s="77">
         <f>$B$4*21</f>
@@ -23499,11 +23880,11 @@
       </c>
       <c r="C20" s="77">
         <f t="shared" si="0"/>
-        <v>301.4127422082932</v>
+        <v>309.64352699282279</v>
       </c>
       <c r="D20" s="90">
         <f t="shared" si="1"/>
-        <v>0.28321296358485926</v>
+        <v>0.36285300026582124</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -23523,7 +23904,7 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="76" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B21" s="77">
         <f>$B$4*22</f>
@@ -23531,11 +23912,11 @@
       </c>
       <c r="C21" s="77">
         <f t="shared" si="0"/>
-        <v>315.76572993249766</v>
+        <v>324.38845684962388</v>
       </c>
       <c r="D21" s="90">
         <f t="shared" si="1"/>
-        <v>0.34431834280318618</v>
+        <v>0.42775076218324148</v>
       </c>
       <c r="E21"/>
       <c r="F21"/>
@@ -23555,7 +23936,7 @@
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="76" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B22" s="77">
         <f>$B$4*23</f>
@@ -23563,11 +23944,11 @@
       </c>
       <c r="C22" s="77">
         <f t="shared" si="0"/>
-        <v>330.11871765670207</v>
+        <v>339.13338670642497</v>
       </c>
       <c r="D22" s="90">
         <f t="shared" si="1"/>
-        <v>0.40542372202151289</v>
+        <v>0.49264852410066151</v>
       </c>
       <c r="E22"/>
       <c r="F22"/>
@@ -23587,7 +23968,7 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="76" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B23" s="77">
         <f>$B$4*24</f>
@@ -23595,11 +23976,11 @@
       </c>
       <c r="C23" s="77">
         <f t="shared" si="0"/>
-        <v>344.47170538090654</v>
+        <v>353.87831656322601</v>
       </c>
       <c r="D23" s="90">
         <f t="shared" si="1"/>
-        <v>0.46652910123983937</v>
+        <v>0.55754628601808154</v>
       </c>
       <c r="E23"/>
       <c r="F23"/>
@@ -23619,7 +24000,7 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="76" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B24" s="77">
         <f>$B$4*25</f>
@@ -23627,11 +24008,11 @@
       </c>
       <c r="C24" s="77">
         <f t="shared" si="0"/>
-        <v>358.82469310511095</v>
+        <v>368.6232464200271</v>
       </c>
       <c r="D24" s="90">
         <f t="shared" si="1"/>
-        <v>0.52763448045816586</v>
+        <v>0.62244404793550157</v>
       </c>
       <c r="E24"/>
       <c r="F24"/>
@@ -23651,7 +24032,7 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="76" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B25" s="77">
         <f>$B$4*26</f>
@@ -23659,11 +24040,11 @@
       </c>
       <c r="C25" s="77">
         <f t="shared" si="0"/>
-        <v>373.17768082931536</v>
+        <v>383.36817627682819</v>
       </c>
       <c r="D25" s="90">
         <f t="shared" si="1"/>
-        <v>0.58873985967649256</v>
+        <v>0.68734180985292137</v>
       </c>
       <c r="E25"/>
       <c r="F25"/>
@@ -23683,7 +24064,7 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="76" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B26" s="77">
         <f>$B$4*27</f>
@@ -23691,11 +24072,11 @@
       </c>
       <c r="C26" s="77">
         <f t="shared" si="0"/>
-        <v>387.53066855351983</v>
+        <v>398.11310613362929</v>
       </c>
       <c r="D26" s="90">
         <f t="shared" si="1"/>
-        <v>0.64984523889481927</v>
+        <v>0.75223957177034184</v>
       </c>
       <c r="E26"/>
       <c r="F26"/>
@@ -23715,7 +24096,7 @@
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="76" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B27" s="77">
         <f>$B$4*28</f>
@@ -23723,11 +24104,11 @@
       </c>
       <c r="C27" s="77">
         <f t="shared" si="0"/>
-        <v>401.8836562777243</v>
+        <v>412.85803599043038</v>
       </c>
       <c r="D27" s="90">
         <f t="shared" si="1"/>
-        <v>0.71095061811314597</v>
+        <v>0.81713733368776165</v>
       </c>
       <c r="E27"/>
       <c r="F27"/>
@@ -23747,7 +24128,7 @@
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="76" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B28" s="77">
         <f>$B$4*29</f>
@@ -23755,11 +24136,11 @@
       </c>
       <c r="C28" s="77">
         <f t="shared" si="0"/>
-        <v>416.23664400192871</v>
+        <v>427.60296584723142</v>
       </c>
       <c r="D28" s="90">
         <f t="shared" si="1"/>
-        <v>0.77205599733147245</v>
+        <v>0.88203509560518167</v>
       </c>
       <c r="E28"/>
       <c r="F28"/>
@@ -23779,7 +24160,7 @@
     </row>
     <row r="29" spans="1:20" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="80" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B29" s="81">
         <f>$B$4*30</f>
@@ -23787,11 +24168,11 @@
       </c>
       <c r="C29" s="81">
         <f t="shared" si="0"/>
-        <v>430.58963172613318</v>
+        <v>442.34789570403257</v>
       </c>
       <c r="D29" s="92">
         <f t="shared" si="1"/>
-        <v>0.83316137654979938</v>
+        <v>0.94693285752260214</v>
       </c>
       <c r="E29"/>
       <c r="F29"/>

--- a/Schibsted modell.xlsx
+++ b/Schibsted modell.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/augusthodt/Desktop/Aksjemodellering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBF1C615-B6D7-CA42-A4FB-0AE5F6A18F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED680BD-CB2C-8D4C-B1A8-AEBCAA549013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17220" activeTab="1" xr2:uid="{CF2EC152-6970-7944-95E4-562C87096A91}"/>
+    <workbookView xWindow="25120" yWindow="500" windowWidth="26080" windowHeight="26740" xr2:uid="{CF2EC152-6970-7944-95E4-562C87096A91}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -283,7 +283,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="350">
   <si>
     <t>Kapitalstruktur</t>
   </si>
@@ -1427,6 +1427,12 @@
   </si>
   <si>
     <t>14.09.26: Vend kjøper tilbake 328 000 aksjer</t>
+  </si>
+  <si>
+    <t>21.09.26: Vend kjøper tilbake 420 000 aksjer</t>
+  </si>
+  <si>
+    <t>28.09.26: Vend kjøper tilbake 500 000 aksjer</t>
   </si>
 </sst>
 </file>
@@ -1884,7 +1890,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2034,7 +2040,8 @@
     </xf>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperkobling" xfId="1" builtinId="8"/>
@@ -3273,7 +3280,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17698142-E94C-684E-8A27-765BEE6464F1}">
-  <dimension ref="A1:AA86"/>
+  <dimension ref="A1:AA88"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.83203125" style="1" bestFit="1" customWidth="1"/>
@@ -3526,7 +3533,7 @@
       </c>
       <c r="W14" s="14">
         <f>SUM(V8:V149)</f>
-        <v>17830530</v>
+        <v>18750530</v>
       </c>
       <c r="X14" s="14">
         <f>532167563-Y13</f>
@@ -3896,7 +3903,7 @@
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="N27" s="48" t="s">
         <v>319</v>
@@ -3913,7 +3920,7 @@
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="T28" s="1" t="s">
         <v>336</v>
@@ -3937,8 +3944,8 @@
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A29" s="67" t="s">
-        <v>340</v>
+      <c r="A29" s="1" t="s">
+        <v>347</v>
       </c>
       <c r="U29" s="93">
         <v>46160</v>
@@ -3961,7 +3968,7 @@
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="U30" s="93">
         <v>46168</v>
@@ -3982,8 +3989,8 @@
       </c>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>338</v>
+      <c r="A31" s="67" t="s">
+        <v>340</v>
       </c>
       <c r="U31" s="93">
         <v>46174</v>
@@ -4005,7 +4012,7 @@
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="U32" s="93">
         <v>46181</v>
@@ -4027,7 +4034,7 @@
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="U33" s="93">
         <v>46188</v>
@@ -4049,8 +4056,9 @@
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>332</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="T34" s="14"/>
       <c r="U34" s="93">
         <v>46195</v>
       </c>
@@ -4071,7 +4079,7 @@
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="U35" s="93">
         <v>46202</v>
@@ -4093,8 +4101,9 @@
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>330</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="T36" s="14"/>
       <c r="U36" s="93">
         <v>46209</v>
       </c>
@@ -4115,7 +4124,7 @@
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="U37" s="93">
         <v>46216</v>
@@ -4137,7 +4146,7 @@
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="U38" s="93">
         <v>46223</v>
@@ -4159,7 +4168,7 @@
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="U39" s="93">
         <v>46230</v>
@@ -4181,7 +4190,7 @@
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="U40" s="93">
         <v>46237</v>
@@ -4204,7 +4213,7 @@
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="U41" s="93">
         <v>46240</v>
@@ -4226,8 +4235,8 @@
       <c r="AA41" s="69"/>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A42" s="67" t="s">
-        <v>287</v>
+      <c r="A42" s="1" t="s">
+        <v>311</v>
       </c>
       <c r="U42" s="122"/>
       <c r="V42" s="123"/>
@@ -4238,7 +4247,7 @@
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>286</v>
+        <v>309</v>
       </c>
       <c r="T43" s="1" t="s">
         <v>337</v>
@@ -4262,8 +4271,8 @@
       </c>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>285</v>
+      <c r="A44" s="67" t="s">
+        <v>287</v>
       </c>
       <c r="U44" s="93">
         <v>46251</v>
@@ -4285,7 +4294,7 @@
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="U45" s="93">
         <v>46258</v>
@@ -4307,7 +4316,7 @@
     </row>
     <row r="46" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N46" s="1" t="s">
         <v>274</v>
@@ -4332,7 +4341,7 @@
     </row>
     <row r="47" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="U47" s="93">
         <v>46272</v>
@@ -4354,13 +4363,13 @@
     </row>
     <row r="48" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N48" s="1" t="s">
         <v>276</v>
       </c>
       <c r="U48" s="93">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="V48" s="14">
         <v>328000</v>
@@ -4377,199 +4386,243 @@
         <v>513563833</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N49" s="1" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="U49" s="93">
+        <v>46286</v>
+      </c>
+      <c r="V49" s="14">
+        <v>420000</v>
+      </c>
+      <c r="W49" s="14">
+        <f>SUM(V43:V49)</f>
+        <v>2480000</v>
+      </c>
+      <c r="X49" s="14">
+        <v>98741830</v>
+      </c>
+      <c r="Y49" s="14">
+        <f>SUM(X43:X49)</f>
+        <v>612305663</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+      <c r="U50" s="93">
+        <v>46293</v>
+      </c>
+      <c r="V50" s="14">
+        <v>500000</v>
+      </c>
+      <c r="W50" s="14">
+        <f>SUM(V43:V50)</f>
+        <v>2980000</v>
+      </c>
+      <c r="X50" s="14">
+        <v>109826562</v>
+      </c>
+      <c r="Y50" s="14">
+        <f>SUM(X43:X50)</f>
+        <v>722132225</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>312</v>
+        <v>280</v>
       </c>
       <c r="N51" s="1" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
         <v>228</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>175</v>
+        <v>217</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
         <v>214</v>
       </c>
     </row>
@@ -4726,7 +4779,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="4">
-        <v>237</v>
+        <v>205</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>52</v>
@@ -4816,8 +4869,8 @@
       <c r="A5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="5">
-        <v>201.887</v>
+      <c r="B5" s="126">
+        <v>195.9</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>53</v>
@@ -4909,7 +4962,7 @@
       </c>
       <c r="B6" s="6">
         <f>B4*B5</f>
-        <v>47847.218999999997</v>
+        <v>40159.5</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>54</v>
@@ -5198,7 +5251,7 @@
       </c>
       <c r="B9" s="7">
         <f>B6-B7+B8</f>
-        <v>45869.218999999997</v>
+        <v>38181.5</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>59</v>
@@ -5528,7 +5581,7 @@
       </c>
       <c r="B12" s="40">
         <f>B4/(U65/B5)</f>
-        <v>2.9109459755429823</v>
+        <v>2.4432378171199125</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>34</v>
@@ -6115,8 +6168,8 @@
       <c r="U16" s="14">
         <v>-260</v>
       </c>
-      <c r="V16" s="14"/>
-      <c r="W16" s="14"/>
+      <c r="V16" s="71"/>
+      <c r="W16" s="71"/>
       <c r="X16" s="14"/>
       <c r="Y16" s="14"/>
       <c r="Z16" s="14">
@@ -8544,39 +8597,39 @@
       </c>
       <c r="AH31" s="9">
         <f t="shared" si="45"/>
-        <v>8.0238526013066735</v>
+        <v>8.2690736606431869</v>
       </c>
       <c r="AI31" s="9">
         <f t="shared" si="45"/>
-        <v>10.618665160256976</v>
+        <v>10.943187612091883</v>
       </c>
       <c r="AJ31" s="9">
         <f t="shared" si="45"/>
-        <v>14.090844342419429</v>
+        <v>14.521481836437117</v>
       </c>
       <c r="AK31" s="9">
         <f t="shared" si="45"/>
-        <v>16.78328491286787</v>
+        <v>17.296207458928819</v>
       </c>
       <c r="AL31" s="9">
         <f t="shared" si="45"/>
-        <v>19.922573773114337</v>
+        <v>20.531437730131362</v>
       </c>
       <c r="AM31" s="9">
         <f t="shared" si="45"/>
-        <v>23.578074438355699</v>
+        <v>24.298656019072574</v>
       </c>
       <c r="AN31" s="9">
         <f t="shared" si="45"/>
-        <v>27.82952505980569</v>
+        <v>28.680037395349625</v>
       </c>
       <c r="AO31" s="9">
         <f t="shared" si="45"/>
-        <v>32.768555742284676</v>
+        <v>33.770012318236986</v>
       </c>
       <c r="AP31" s="9">
         <f t="shared" si="45"/>
-        <v>38.500424637600958</v>
+        <v>39.677055787704674</v>
       </c>
     </row>
     <row r="32" spans="3:159" x14ac:dyDescent="0.25">
@@ -8637,7 +8690,9 @@
       <c r="U32" s="8">
         <v>201.887</v>
       </c>
-      <c r="V32" s="8"/>
+      <c r="V32" s="8">
+        <v>195.9</v>
+      </c>
       <c r="W32" s="8"/>
       <c r="X32" s="8"/>
       <c r="Z32" s="8">
@@ -8665,31 +8720,31 @@
         <v>201.887</v>
       </c>
       <c r="AH32" s="8">
-        <v>201.887</v>
+        <v>195.9</v>
       </c>
       <c r="AI32" s="8">
-        <v>201.887</v>
+        <v>195.9</v>
       </c>
       <c r="AJ32" s="8">
-        <v>201.887</v>
+        <v>195.9</v>
       </c>
       <c r="AK32" s="8">
-        <v>201.887</v>
+        <v>195.9</v>
       </c>
       <c r="AL32" s="8">
-        <v>201.887</v>
+        <v>195.9</v>
       </c>
       <c r="AM32" s="8">
-        <v>201.887</v>
+        <v>195.9</v>
       </c>
       <c r="AN32" s="8">
-        <v>201.887</v>
+        <v>195.9</v>
       </c>
       <c r="AO32" s="8">
-        <v>201.887</v>
+        <v>195.9</v>
       </c>
       <c r="AP32" s="8">
-        <v>201.887</v>
+        <v>195.9</v>
       </c>
     </row>
     <row r="33" spans="2:45" x14ac:dyDescent="0.25">
@@ -9163,7 +9218,7 @@
         <v>186</v>
       </c>
       <c r="AS36" s="8">
-        <v>201.887</v>
+        <v>195.9</v>
       </c>
     </row>
     <row r="37" spans="2:45" x14ac:dyDescent="0.25">
@@ -9324,7 +9379,7 @@
       </c>
       <c r="AS37" s="46">
         <f>AS35/AS36</f>
-        <v>287.85769499502044</v>
+        <v>296.65506109984528</v>
       </c>
     </row>
     <row r="38" spans="2:45" x14ac:dyDescent="0.25">
@@ -9371,7 +9426,7 @@
       </c>
       <c r="AS38" s="41">
         <f>(AS37-B4)/B4</f>
-        <v>0.21458943035873604</v>
+        <v>0.44709785902363552</v>
       </c>
     </row>
     <row r="39" spans="2:45" x14ac:dyDescent="0.25">
@@ -16039,7 +16094,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55B37E73-D66F-CD46-BE03-0F584F4CABDA}">
-  <dimension ref="A2:F101"/>
+  <dimension ref="A2:G1048576"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
@@ -16103,7 +16158,7 @@
       </c>
       <c r="F6" s="119">
         <f>E6/Modell!$B$5</f>
-        <v>128.28958773967616</v>
+        <v>132.21031138335886</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -16122,7 +16177,7 @@
       </c>
       <c r="F7" s="119">
         <f>E7/Modell!$B$5</f>
-        <v>65.888343479273061</v>
+        <v>67.901990811638584</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -16141,7 +16196,7 @@
       </c>
       <c r="F8" s="119">
         <f>E8/Modell!$B$5</f>
-        <v>65.97750226611916</v>
+        <v>67.993874425727412</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -16160,7 +16215,7 @@
       </c>
       <c r="F9" s="119">
         <f>E9/Modell!$B$5</f>
-        <v>-3.9626127487158658</v>
+        <v>-4.0837161817253698</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -16179,7 +16234,7 @@
       </c>
       <c r="F10" s="119">
         <f>E10/Modell!$B$5</f>
-        <v>-16.940169500760327</v>
+        <v>-17.457886676875958</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -16200,7 +16255,7 @@
       </c>
       <c r="F11" s="120">
         <f>SUM(F6:F10)</f>
-        <v>239.2526512355922</v>
+        <v>246.56457376212353</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -16226,7 +16281,7 @@
       </c>
       <c r="F13" s="119">
         <f>E13/Modell!B5</f>
-        <v>153.94750528761139</v>
+        <v>158.65237366003063</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -16240,7 +16295,7 @@
       </c>
       <c r="F14" s="119">
         <f>E14/Modell!B5</f>
-        <v>-24.766329679474161</v>
+        <v>-25.523226135783563</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -16255,7 +16310,7 @@
       </c>
       <c r="F15" s="120">
         <f>SUM(F13:F14)</f>
-        <v>129.18117560813724</v>
+        <v>133.12914752424706</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -16265,7 +16320,7 @@
       <c r="E16" s="121"/>
       <c r="F16" s="121"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="48" t="s">
         <v>326</v>
       </c>
@@ -16277,10 +16332,10 @@
       </c>
       <c r="F17" s="119">
         <f>E17/Modell!B5</f>
-        <v>20.912688781347981</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+        <v>21.551812149055639</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="48" t="s">
         <v>325</v>
       </c>
@@ -16292,17 +16347,17 @@
       </c>
       <c r="F18" s="119">
         <f>E18/(Modell!B5*-1)</f>
-        <v>-11.115128760148004</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+        <v>-11.454823889739663</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="51"/>
       <c r="C19" s="121"/>
       <c r="D19" s="51"/>
       <c r="E19" s="121"/>
       <c r="F19" s="121"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="49" t="s">
         <v>327</v>
       </c>
@@ -16314,8 +16369,41 @@
       </c>
       <c r="F20" s="120">
         <f>F11+F15+F17+F18</f>
-        <v>378.23138686492939</v>
-      </c>
+        <v>389.79070954568658</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C26" s="14"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="14"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="2"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="125"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="14"/>
     </row>
     <row r="60" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B60" s="52"/>
@@ -16376,7 +16464,7 @@
       </c>
       <c r="B87" s="119">
         <f>F6</f>
-        <v>128.28958773967616</v>
+        <v>132.21031138335886</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -16385,7 +16473,7 @@
       </c>
       <c r="B88" s="119">
         <f t="shared" ref="B88:B101" si="1">F7</f>
-        <v>65.888343479273061</v>
+        <v>67.901990811638584</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -16394,7 +16482,7 @@
       </c>
       <c r="B89" s="119">
         <f t="shared" si="1"/>
-        <v>65.97750226611916</v>
+        <v>67.993874425727412</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -16403,7 +16491,7 @@
       </c>
       <c r="B90" s="119">
         <f t="shared" si="1"/>
-        <v>-3.9626127487158658</v>
+        <v>-4.0837161817253698</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -16412,7 +16500,7 @@
       </c>
       <c r="B91" s="119">
         <f t="shared" si="1"/>
-        <v>-16.940169500760327</v>
+        <v>-17.457886676875958</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
@@ -16421,7 +16509,7 @@
       </c>
       <c r="B92" s="119">
         <f t="shared" si="1"/>
-        <v>239.2526512355922</v>
+        <v>246.56457376212353</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
@@ -16434,7 +16522,7 @@
       </c>
       <c r="B94" s="119">
         <f t="shared" si="1"/>
-        <v>153.94750528761139</v>
+        <v>158.65237366003063</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -16443,7 +16531,7 @@
       </c>
       <c r="B95" s="119">
         <f t="shared" si="1"/>
-        <v>-24.766329679474161</v>
+        <v>-25.523226135783563</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
@@ -16452,7 +16540,7 @@
       </c>
       <c r="B96" s="119">
         <f t="shared" si="1"/>
-        <v>129.18117560813724</v>
+        <v>133.12914752424706</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
@@ -16465,7 +16553,7 @@
       </c>
       <c r="B98" s="119">
         <f t="shared" si="1"/>
-        <v>20.912688781347981</v>
+        <v>21.551812149055639</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
@@ -16474,7 +16562,7 @@
       </c>
       <c r="B99" s="119">
         <f t="shared" si="1"/>
-        <v>-11.115128760148004</v>
+        <v>-11.454823889739663</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
@@ -16487,7 +16575,13 @@
       </c>
       <c r="B101" s="119">
         <f t="shared" si="1"/>
-        <v>378.23138686492939</v>
+        <v>389.79070954568658</v>
+      </c>
+    </row>
+    <row r="1048576" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C1048576" s="1">
+        <f>C1048548*1.2</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -21940,13 +22034,13 @@
         <v>4.6052631578947366E-2</v>
       </c>
       <c r="Z6" s="103"/>
-      <c r="AA6" s="125">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="125">
+      <c r="AA6" s="101">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="101">
         <v>0.03</v>
       </c>
-      <c r="AC6" s="125">
+      <c r="AC6" s="101">
         <v>0.04</v>
       </c>
     </row>
@@ -23277,15 +23371,15 @@
       </c>
       <c r="D5" s="42">
         <f>Modell!$B$9/Modell!AG17</f>
-        <v>18.968635755134937</v>
+        <v>15.789476731327923</v>
       </c>
       <c r="E5" s="56">
         <f>Modell!$B$9/Modell!AH17</f>
-        <v>15.408851868766476</v>
+        <v>12.82631556528807</v>
       </c>
       <c r="F5" s="59">
         <f>Modell!$B$9/Modell!AI17</f>
-        <v>12.299278174550574</v>
+        <v>10.237908991247547</v>
       </c>
     </row>
     <row r="6" spans="3:6" ht="62" x14ac:dyDescent="0.7">
@@ -23294,15 +23388,15 @@
       </c>
       <c r="D6" s="42">
         <f>Modell!$B$9/Modell!AG22</f>
-        <v>30.21366835089713</v>
+        <v>25.149832573774123</v>
       </c>
       <c r="E6" s="56">
         <f>Modell!$B$9/Modell!AH22</f>
-        <v>22.08638567894484</v>
+        <v>18.384689192127567</v>
       </c>
       <c r="F6" s="59">
         <f>Modell!$B$9/Modell!AI22</f>
-        <v>16.689282551892358</v>
+        <v>13.892145008073454</v>
       </c>
     </row>
     <row r="7" spans="3:6" ht="62" x14ac:dyDescent="0.7">
@@ -23311,15 +23405,15 @@
       </c>
       <c r="D7" s="42">
         <f>Modell!$B$4/Modell!AG31</f>
-        <v>40.40584653430642</v>
+        <v>34.950204808155341</v>
       </c>
       <c r="E7" s="56">
         <f>Modell!$B$4/Modell!AH31</f>
-        <v>29.536933412934939</v>
+        <v>24.791168686246127</v>
       </c>
       <c r="F7" s="58">
         <f>Modell!$B$4/Modell!AI31</f>
-        <v>22.319189504819501</v>
+        <v>18.733115730692706</v>
       </c>
     </row>
   </sheetData>
@@ -23446,7 +23540,7 @@
       </c>
       <c r="B6" s="61">
         <f>Modell!B9</f>
-        <v>45869.218999999997</v>
+        <v>38181.5</v>
       </c>
       <c r="C6"/>
       <c r="D6"/>
@@ -23532,7 +23626,7 @@
       </c>
       <c r="D9" s="89">
         <f>B9/$B$6-1</f>
-        <v>-0.3510223808257994</v>
+        <v>-0.22035287927399383</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -23564,7 +23658,7 @@
       </c>
       <c r="D10" s="90">
         <f t="shared" ref="D10:D29" si="1">B10/$B$6-1</f>
-        <v>-0.28612461890837926</v>
+        <v>-0.14238816720139313</v>
       </c>
       <c r="E10"/>
       <c r="F10"/>
@@ -23596,7 +23690,7 @@
       </c>
       <c r="D11" s="90">
         <f t="shared" si="1"/>
-        <v>-0.22122685699095923</v>
+        <v>-6.4423455128792551E-2</v>
       </c>
       <c r="E11"/>
       <c r="F11"/>
@@ -23628,7 +23722,7 @@
       </c>
       <c r="D12" s="90">
         <f t="shared" si="1"/>
-        <v>-0.15632909507353931</v>
+        <v>1.3541256943808033E-2</v>
       </c>
       <c r="E12"/>
       <c r="F12"/>
@@ -23660,7 +23754,7 @@
       </c>
       <c r="D13" s="90">
         <f t="shared" si="1"/>
-        <v>-9.1431333156119177E-2</v>
+        <v>9.1505969016408617E-2</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -23692,7 +23786,7 @@
       </c>
       <c r="D14" s="90">
         <f t="shared" si="1"/>
-        <v>-2.6533571238698928E-2</v>
+        <v>0.16947068108900942</v>
       </c>
       <c r="E14"/>
       <c r="F14"/>
@@ -23724,7 +23818,7 @@
       </c>
       <c r="D15" s="90">
         <f>B15/$B$6-1</f>
-        <v>3.83641906787211E-2</v>
+        <v>0.24743539316161001</v>
       </c>
       <c r="E15"/>
       <c r="F15"/>
@@ -23756,7 +23850,7 @@
       </c>
       <c r="D16" s="90">
         <f t="shared" si="1"/>
-        <v>0.1032619525961409</v>
+        <v>0.32540010523421037</v>
       </c>
       <c r="E16"/>
       <c r="F16"/>
@@ -23788,7 +23882,7 @@
       </c>
       <c r="D17" s="90">
         <f t="shared" si="1"/>
-        <v>0.16815971451356115</v>
+        <v>0.40336481730681117</v>
       </c>
       <c r="E17"/>
       <c r="F17"/>
@@ -23820,7 +23914,7 @@
       </c>
       <c r="D18" s="90">
         <f t="shared" si="1"/>
-        <v>0.23305747643098118</v>
+        <v>0.48132952937941198</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -23852,7 +23946,7 @@
       </c>
       <c r="D19" s="91">
         <f t="shared" si="1"/>
-        <v>0.29795523834840121</v>
+        <v>0.55929424145201234</v>
       </c>
       <c r="E19"/>
       <c r="F19"/>
@@ -23884,7 +23978,7 @@
       </c>
       <c r="D20" s="90">
         <f t="shared" si="1"/>
-        <v>0.36285300026582124</v>
+        <v>0.63725895352461293</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -23916,7 +24010,7 @@
       </c>
       <c r="D21" s="90">
         <f t="shared" si="1"/>
-        <v>0.42775076218324148</v>
+        <v>0.71522366559721373</v>
       </c>
       <c r="E21"/>
       <c r="F21"/>
@@ -23948,7 +24042,7 @@
       </c>
       <c r="D22" s="90">
         <f t="shared" si="1"/>
-        <v>0.49264852410066151</v>
+        <v>0.79318837766981432</v>
       </c>
       <c r="E22"/>
       <c r="F22"/>
@@ -23980,7 +24074,7 @@
       </c>
       <c r="D23" s="90">
         <f t="shared" si="1"/>
-        <v>0.55754628601808154</v>
+        <v>0.8711530897424149</v>
       </c>
       <c r="E23"/>
       <c r="F23"/>
@@ -24012,7 +24106,7 @@
       </c>
       <c r="D24" s="90">
         <f t="shared" si="1"/>
-        <v>0.62244404793550157</v>
+        <v>0.94911780181501548</v>
       </c>
       <c r="E24"/>
       <c r="F24"/>
@@ -24044,7 +24138,7 @@
       </c>
       <c r="D25" s="90">
         <f t="shared" si="1"/>
-        <v>0.68734180985292137</v>
+        <v>1.0270825138876161</v>
       </c>
       <c r="E25"/>
       <c r="F25"/>
@@ -24076,7 +24170,7 @@
       </c>
       <c r="D26" s="90">
         <f t="shared" si="1"/>
-        <v>0.75223957177034184</v>
+        <v>1.1050472259602167</v>
       </c>
       <c r="E26"/>
       <c r="F26"/>
@@ -24108,7 +24202,7 @@
       </c>
       <c r="D27" s="90">
         <f t="shared" si="1"/>
-        <v>0.81713733368776165</v>
+        <v>1.1830119380328172</v>
       </c>
       <c r="E27"/>
       <c r="F27"/>
@@ -24140,7 +24234,7 @@
       </c>
       <c r="D28" s="90">
         <f t="shared" si="1"/>
-        <v>0.88203509560518167</v>
+        <v>1.2609766501054178</v>
       </c>
       <c r="E28"/>
       <c r="F28"/>
@@ -24172,7 +24266,7 @@
       </c>
       <c r="D29" s="92">
         <f t="shared" si="1"/>
-        <v>0.94693285752260214</v>
+        <v>1.3389413621780188</v>
       </c>
       <c r="E29"/>
       <c r="F29"/>
